--- a/Kachi_Gun/Table/String.xlsx
+++ b/Kachi_Gun/Table/String.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C286"/>
+  <dimension ref="A1:C355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -896,12 +896,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>모든 단계를 끝냈습니다</t>
+          <t>다이아</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>All tiers completed</t>
+          <t>Gems</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>아직 달성하지 못했습니다</t>
+          <t>모든 단계를 끝냈습니다</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Not achieved yet</t>
+          <t>All tiers completed</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>다이아</t>
+          <t>아직 달성하지 못했습니다</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Gems</t>
+          <t>Not achieved yet</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>리볼버</t>
+          <t>기본탄_D</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Revolver</t>
+          <t>Basic Round_D</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -3276,12 +3276,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>소드오프 샷건</t>
+          <t>산탄_D</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Sawed-off Shotgun</t>
+          <t>Buckshot_D</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>우지</t>
+          <t>속사탄_D</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Uzi</t>
+          <t>Rapid Round_D</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>상위 리볼버</t>
+          <t>기본탄_C</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Elite Revolver</t>
+          <t>Basic Round_C</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>펌프액션 샷건</t>
+          <t>산탄_C</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Pump Shotgun</t>
+          <t>Buckshot_C</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>돌격소총</t>
+          <t>관통탄_C</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Piercing Round_C</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>매그넘</t>
+          <t>기본탄_B</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Magnum</t>
+          <t>Basic Round_B</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>전투 샷건</t>
+          <t>산탄_B</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Combat Shotgun</t>
+          <t>Buckshot_B</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>중기관총</t>
+          <t>속사탄_B</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Heavy MG</t>
+          <t>Rapid Round_B</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -3412,12 +3412,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>관통 라이플</t>
+          <t>관통탄_B</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Piercing Rifle</t>
+          <t>Piercing Round_B</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>황금 매그넘</t>
+          <t>기본탄_A</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Golden Magnum</t>
+          <t>Basic Round_A</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>드래곤 샷건</t>
+          <t>산탄_A</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Dragon Shotgun</t>
+          <t>Buckshot_A</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>미니건</t>
+          <t>속사탄_A</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Minigun</t>
+          <t>Rapid Round_A</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>레일 라이플</t>
+          <t>관통탄_A</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Rail Rifle</t>
+          <t>Piercing Round_A</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -3497,12 +3497,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>레이저 건</t>
+          <t>기본탄_S</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Laser Gun</t>
+          <t>Basic Round_S</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>미사일 런처</t>
+          <t>산탄_S</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Missile Launcher</t>
+          <t>Buckshot_S</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>플라즈마 레이저</t>
+          <t>속사탄_S</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Plasma Laser</t>
+          <t>Rapid Round_S</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>다연장 미사일</t>
+          <t>관통탄_S</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Multi Missile</t>
+          <t>Piercing Round_S</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>오메가 레이저</t>
+          <t>레이저탄_S</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Omega Laser</t>
+          <t>Laser Round_S</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>핵 미사일</t>
+          <t>미사일탄_S</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Nuke Missile</t>
+          <t>Missile_S</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>하이퍼 레이저</t>
+          <t>기본탄_SS</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Hyper Laser</t>
+          <t>Basic Round_SS</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>전술 핵 미사일</t>
+          <t>산탄_SS</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Tactical Nuke</t>
+          <t>Buckshot_SS</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>퀘이사 레이저</t>
+          <t>속사탄_SS</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Quasar Laser</t>
+          <t>Rapid Round_SS</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>반물질 미사일</t>
+          <t>관통탄_SS</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Antimatter Missile</t>
+          <t>Piercing Round_SS</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>네뷸라 레이저</t>
+          <t>레이저탄_SS</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Nebula Laser</t>
+          <t>Laser Round_SS</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>중력자 미사일</t>
+          <t>미사일탄_SS</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Graviton Missile</t>
+          <t>Missile_SS</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>노바 레이저</t>
+          <t>기본탄_SSS</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Nova Laser</t>
+          <t>Basic Round_SSS</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>초신성 미사일</t>
+          <t>산탄_SSS</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Supernova Missile</t>
+          <t>Buckshot_SSS</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>보이드 레이저</t>
+          <t>속사탄_SSS</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Void Laser</t>
+          <t>Rapid Round_SSS</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>차원파괴 미사일</t>
+          <t>관통탄_SSS</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Rift Missile</t>
+          <t>Piercing Round_SSS</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>제네시스 레이저</t>
+          <t>레이저탄_SSS</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Genesis Laser</t>
+          <t>Laser Round_SSS</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>아포칼립스 미사일</t>
+          <t>미사일탄_SSS</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Apocalypse Missile</t>
+          <t>Missile_SSS</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -3803,1496 +3803,2669 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>기어오는 좀비</t>
+          <t>기본탄_R</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Crawler</t>
+          <t>Basic Round_R</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>칼 좀비</t>
+          <t>산탄_R</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Knife Zombie</t>
+          <t>Buckshot_R</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>좀비</t>
+          <t>속사탄_R</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Zombie</t>
+          <t>Rapid Round_R</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>모자 좀비</t>
+          <t>관통탄_R</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Hat Zombie</t>
+          <t>Piercing Round_R</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>양동이 좀비</t>
+          <t>레이저탄_R</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Bucket Zombie</t>
+          <t>Laser Round_R</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>갑옷 좀비</t>
+          <t>미사일탄_R</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Armored Zombie</t>
+          <t>Missile_R</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>방망이 좀비</t>
+          <t>기본탄_SR</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Bat Zombie</t>
+          <t>Basic Round_SR</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>농부 좀비</t>
+          <t>산탄_SR</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Farmer Zombie</t>
+          <t>Buckshot_SR</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>미라</t>
+          <t>속사탄_SR</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Mummy</t>
+          <t>Rapid Round_SR</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>뚱보 좀비</t>
+          <t>관통탄_SR</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Fat Zombie</t>
+          <t>Piercing Round_SR</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>사신 좀비</t>
+          <t>레이저탄_SR</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Reaper Zombie</t>
+          <t>Laser Round_SR</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>변이 오우거</t>
+          <t>미사일탄_SR</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Mutant Ogre</t>
+          <t>Missile_SR</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>비상 건빵</t>
+          <t>기본탄_SSR</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Emergency Crackers</t>
+          <t>Basic Round_SSR</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>통조림 캔</t>
+          <t>산탄_SSR</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Canned Food</t>
+          <t>Buckshot_SSR</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>정수 필터</t>
+          <t>속사탄_SSR</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Water Filter</t>
+          <t>Rapid Round_SSR</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>야전 반합</t>
+          <t>관통탄_SSR</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Mess Kit</t>
+          <t>Piercing Round_SSR</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>에너지 바</t>
+          <t>레이저탄_SSR</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Energy Bar</t>
+          <t>Laser Round_SSR</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>구급 상자</t>
+          <t>미사일탄_SSR</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Missile_SSR</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>아드레날린 주사</t>
+          <t>기본탄_U</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Adrenaline Shot</t>
+          <t>Basic Round_U</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>군용 무전기</t>
+          <t>산탄_U</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Field Radio</t>
+          <t>Buckshot_U</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>야간 투시경</t>
+          <t>속사탄_U</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Night Vision</t>
+          <t>Rapid Round_U</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>방탄 조끼</t>
+          <t>관통탄_U</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Bulletproof Vest</t>
+          <t>Piercing Round_U</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>전술 탄띠</t>
+          <t>레이저탄_U</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Tactical Bandolier</t>
+          <t>Laser Round_U</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>고농축 스팀팩</t>
+          <t>미사일탄_U</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Mega Stimpack</t>
+          <t>Missile_U</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>열화우라늄 탄심</t>
+          <t>기본탄_SU</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>DU Core</t>
+          <t>Basic Round_SU</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>냉각 모듈</t>
+          <t>산탄_SU</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Cooling Module</t>
+          <t>Buckshot_SU</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>플라즈마 배터리</t>
+          <t>속사탄_SU</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Plasma Battery</t>
+          <t>Rapid Round_SU</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>양자 증폭기</t>
+          <t>관통탄_SU</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Quantum Amplifier</t>
+          <t>Piercing Round_SU</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>중력 제어 코어</t>
+          <t>레이저탄_SU</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Gravity Core</t>
+          <t>Laser Round_SU</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>나노 수복 혈청</t>
+          <t>미사일탄_SU</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Nano Serum</t>
+          <t>Missile_SU</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>바이오 리액터</t>
+          <t>기본탄_SSU</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Bio Reactor</t>
+          <t>Basic Round_SSU</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>초전도 코일</t>
+          <t>산탄_SSU</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Superconductor Coil</t>
+          <t>Buckshot_SSU</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>암흑물질 셀</t>
+          <t>속사탄_SSU</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Dark Matter Cell</t>
+          <t>Rapid Round_SSU</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>차원 도약 엔진</t>
+          <t>관통탄_SSU</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Warp Engine</t>
+          <t>Piercing Round_SSU</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>항성 에너지 핵</t>
+          <t>레이저탄_SSU</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Stellar Core</t>
+          <t>Laser Round_SSU</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>영구기관 모듈</t>
+          <t>미사일탄_SSU</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Perpetual Engine</t>
+          <t>Missile_SSU</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>카피바라의 성배</t>
+          <t>기어오는 좀비</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Capybara Grail</t>
+          <t>Crawler</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>태초</t>
+          <t>칼 좀비</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Primordial</t>
+          <t>Knife Zombie</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Grade</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>좀비 처치하기</t>
+          <t>좀비</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Defeat zombies</t>
+          <t>Zombie</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>스테이지 클리어하기</t>
+          <t>모자 좀비</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Clear stages</t>
+          <t>Hat Zombie</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>광산 플레이하기</t>
+          <t>양동이 좀비</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Play the mine</t>
+          <t>Bucket Zombie</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>보스 처치하기</t>
+          <t>갑옷 좀비</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Defeat bosses</t>
+          <t>Armored Zombie</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>총알 합성하기</t>
+          <t>방망이 좀비</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Merge ammo</t>
+          <t>Bat Zombie</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>공격력 x2 (5분)</t>
+          <t>농부 좀비</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Attack x2 (5 min)</t>
+          <t>Farmer Zombie</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>광고 1편 · 연속 시청 시 시간 누적</t>
+          <t>미라</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>1 ad · time stacks when watched again</t>
+          <t>Mummy</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>돈 획득량 x2 (5분)</t>
+          <t>뚱보 좀비</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Gold x2 (5 min)</t>
+          <t>Fat Zombie</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>강제 광고 제거</t>
+          <t>사신 좀비</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Remove Forced Ads</t>
+          <t>Reaper Zombie</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>자동 전면 광고 제거 + 돼지저금통</t>
+          <t>변이 오우거</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>No more forced ads + piggy bank</t>
+          <t>Mutant Ogre</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>모든 광고 제거</t>
+          <t>비상 건빵</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Remove All Ads</t>
+          <t>Emergency Crackers</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>보상형 광고도 바로 보상</t>
+          <t>통조림 캔</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Rewards without watching ads</t>
+          <t>Canned Food</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>자동강화 패키지</t>
+          <t>정수 필터</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Auto Upgrade Pack</t>
+          <t>Water Filter</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>하단 강화 자동 + 다이아 500</t>
+          <t>야전 반합</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Upgrades buy themselves + 500 gems</t>
+          <t>Mess Kit</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>영구 3배 버프</t>
+          <t>에너지 바</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Permanent x3 Buff</t>
+          <t>Energy Bar</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
+          <t>구급 상자</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Permanent x3 attack &amp; gold + 1,000 gems</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>광산 티켓 확장</t>
+          <t>아드레날린 주사</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Mine Ticket Pack</t>
+          <t>Adrenaline Shot</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
+          <t>군용 무전기</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Daily mine tickets 2 → 6 + 500 gems</t>
+          <t>Field Radio</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>핫딜 레이저 총알</t>
+          <t>야간 투시경</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Hot Deal: Laser Ammo</t>
+          <t>Night Vision</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>S 등급 레이저 건 즉시 지급</t>
+          <t>방탄 조끼</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Get an S grade Laser Gun now</t>
+          <t>Bulletproof Vest</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>다이아 한 줌 (500)</t>
+          <t>전술 탄띠</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Handful of Gems (500)</t>
+          <t>Tactical Bandolier</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>다이아 500개 즉시 획득</t>
+          <t>고농축 스팀팩</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Get 500 gems now</t>
+          <t>Mega Stimpack</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>다이아 주머니 (1,800)</t>
+          <t>열화우라늄 탄심</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Pouch of Gems (1,800)</t>
+          <t>DU Core</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>다이아 1,800개 즉시 획득</t>
+          <t>냉각 모듈</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Get 1,800 gems now</t>
+          <t>Cooling Module</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>다이아 상자 (4,200)</t>
+          <t>플라즈마 배터리</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Chest of Gems (4,200)</t>
+          <t>Plasma Battery</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>다이아 4,200개 즉시 획득</t>
+          <t>양자 증폭기</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Get 4,200 gems now</t>
+          <t>Quantum Amplifier</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>30분 방치 골드 상자</t>
+          <t>중력 제어 코어</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>30-min Gold Chest</t>
+          <t>Gravity Core</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>현재 스테이지 기준 600마리 처치 골드</t>
+          <t>나노 수복 혈청</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Gold of 600 zombies at your current stage</t>
+          <t>Nano Serum</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>바이오 리액터</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Free Gems</t>
+          <t>Bio Reactor</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>광고 1편 · 다이아 40 · 하루 3번</t>
+          <t>초전도 코일</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>1 ad · 40 gems · 3 times a day</t>
+          <t>Superconductor Coil</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>폐허 숲길</t>
+          <t>암흑물질 셀</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Ruined Forest Trail</t>
+          <t>Dark Matter Cell</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>오염된 해안</t>
+          <t>차원 도약 엔진</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Polluted Coast</t>
+          <t>Warp Engine</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>사막 도로</t>
+          <t>항성 에너지 핵</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Desert Road</t>
+          <t>Stellar Core</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>얼어붙은 설원</t>
+          <t>영구기관 모듈</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Frozen Snowfield</t>
+          <t>Perpetual Engine</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>지하 연구소</t>
+          <t>카피바라의 성배</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Underground Lab</t>
+          <t>Capybara Grail</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>오염 구역</t>
+          <t>태초</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Contaminated Zone</t>
+          <t>Primordial</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Supply_Collection.Grade</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>무기는 다이아 100 또는 도전 클리어 에서 열립니다</t>
+          <t>좀비 처치하기</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Weapons unlock with 100 gems or a challenge clear</t>
+          <t>Defeat zombies</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>무기 메뉴가 열렸습니다!</t>
+          <t>스테이지 클리어하기</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Weapons unlocked!</t>
+          <t>Clear stages</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>Stage 1-2 에서 열립니다</t>
+          <t>광산 플레이하기</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 1-2</t>
+          <t>Play the mine</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>스킨이 열렸습니다!</t>
+          <t>보스 처치하기</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Skins unlocked!</t>
+          <t>Defeat bosses</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>Stage 4-1 에서 열립니다</t>
+          <t>총알 합성하기</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 4-1</t>
+          <t>Merge ammo</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>다이아 광산이 열렸습니다!</t>
+          <t>공격력 x2 (5분)</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Gem Mine unlocked!</t>
+          <t>Attack x2 (5 min)</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>Stage 6-1 에서 열립니다</t>
+          <t>광고 1편 · 연속 시청 시 시간 누적</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 6-1</t>
+          <t>1 ad · time stacks when watched again</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>보급품이 열렸습니다!</t>
+          <t>돈 획득량 x2 (5분)</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Supplies unlocked!</t>
+          <t>Gold x2 (5 min)</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>Stage 10-1 에서 열립니다</t>
+          <t>강제 광고 제거</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 10-1</t>
+          <t>Remove Forced Ads</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>보스 던전이 열렸습니다!</t>
+          <t>자동 전면 광고 제거 + 돼지저금통</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Boss Dungeon unlocked!</t>
+          <t>No more forced ads + piggy bank</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>큰 푸른 보석</t>
+          <t>모든 광고 제거</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Big Blue Gem</t>
+          <t>Remove All Ads</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>작은 푸른 보석</t>
+          <t>보상형 광고도 바로 보상</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Small Blue Gem</t>
+          <t>Rewards without watching ads</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>회색 바위</t>
+          <t>자동강화 패키지</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Gray Rock</t>
+          <t>Auto Upgrade Pack</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
+          <t>하단 강화 자동 + 다이아 500</t>
+        </is>
+      </c>
+      <c r="B286" s="2" t="inlineStr">
+        <is>
+          <t>Upgrades buy themselves + 500 gems</t>
+        </is>
+      </c>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="inlineStr">
+        <is>
+          <t>영구 3배 버프</t>
+        </is>
+      </c>
+      <c r="B287" s="2" t="inlineStr">
+        <is>
+          <t>Permanent x3 Buff</t>
+        </is>
+      </c>
+      <c r="C287" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Permanent x3 attack &amp; gold + 1,000 gems</t>
+        </is>
+      </c>
+      <c r="C288" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="inlineStr">
+        <is>
+          <t>광산 티켓 확장</t>
+        </is>
+      </c>
+      <c r="B289" s="2" t="inlineStr">
+        <is>
+          <t>Mine Ticket Pack</t>
+        </is>
+      </c>
+      <c r="C289" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="inlineStr">
+        <is>
+          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="inlineStr">
+        <is>
+          <t>Daily mine tickets 2 → 6 + 500 gems</t>
+        </is>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="inlineStr">
+        <is>
+          <t>핫딜 레이저 총알</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="inlineStr">
+        <is>
+          <t>Hot Deal: Laser Ammo</t>
+        </is>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="inlineStr">
+        <is>
+          <t>레이저탄_S 즉시 지급</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="inlineStr">
+        <is>
+          <t>Get a Laser Round_S now</t>
+        </is>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2" t="inlineStr">
+        <is>
+          <t>다이아 한 줌 (500)</t>
+        </is>
+      </c>
+      <c r="B293" s="2" t="inlineStr">
+        <is>
+          <t>Handful of Gems (500)</t>
+        </is>
+      </c>
+      <c r="C293" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2" t="inlineStr">
+        <is>
+          <t>다이아 500개 즉시 획득</t>
+        </is>
+      </c>
+      <c r="B294" s="2" t="inlineStr">
+        <is>
+          <t>Get 500 gems now</t>
+        </is>
+      </c>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2" t="inlineStr">
+        <is>
+          <t>다이아 주머니 (1,800)</t>
+        </is>
+      </c>
+      <c r="B295" s="2" t="inlineStr">
+        <is>
+          <t>Pouch of Gems (1,800)</t>
+        </is>
+      </c>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2" t="inlineStr">
+        <is>
+          <t>다이아 1,800개 즉시 획득</t>
+        </is>
+      </c>
+      <c r="B296" s="2" t="inlineStr">
+        <is>
+          <t>Get 1,800 gems now</t>
+        </is>
+      </c>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2" t="inlineStr">
+        <is>
+          <t>다이아 상자 (4,200)</t>
+        </is>
+      </c>
+      <c r="B297" s="2" t="inlineStr">
+        <is>
+          <t>Chest of Gems (4,200)</t>
+        </is>
+      </c>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2" t="inlineStr">
+        <is>
+          <t>다이아 4,200개 즉시 획득</t>
+        </is>
+      </c>
+      <c r="B298" s="2" t="inlineStr">
+        <is>
+          <t>Get 4,200 gems now</t>
+        </is>
+      </c>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>30분 방치 골드 상자</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>30-min Gold Chest</t>
+        </is>
+      </c>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2" t="inlineStr">
+        <is>
+          <t>현재 스테이지 기준 600마리 처치 골드</t>
+        </is>
+      </c>
+      <c r="B300" s="2" t="inlineStr">
+        <is>
+          <t>Gold of 600 zombies at your current stage</t>
+        </is>
+      </c>
+      <c r="C300" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="2" t="inlineStr">
+        <is>
+          <t>무료 다이아</t>
+        </is>
+      </c>
+      <c r="B301" s="2" t="inlineStr">
+        <is>
+          <t>Free Gems</t>
+        </is>
+      </c>
+      <c r="C301" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="2" t="inlineStr">
+        <is>
+          <t>광고 1편 · 다이아 40 · 하루 3번</t>
+        </is>
+      </c>
+      <c r="B302" s="2" t="inlineStr">
+        <is>
+          <t>1 ad · 40 gems · 3 times a day</t>
+        </is>
+      </c>
+      <c r="C302" s="2" t="inlineStr">
+        <is>
+          <t>Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="2" t="inlineStr">
+        <is>
+          <t>폐허 숲길</t>
+        </is>
+      </c>
+      <c r="B303" s="2" t="inlineStr">
+        <is>
+          <t>Ruined Forest Trail</t>
+        </is>
+      </c>
+      <c r="C303" s="2" t="inlineStr">
+        <is>
+          <t>Chapter_Summary.Biome_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="2" t="inlineStr">
+        <is>
+          <t>오염된 해안</t>
+        </is>
+      </c>
+      <c r="B304" s="2" t="inlineStr">
+        <is>
+          <t>Polluted Coast</t>
+        </is>
+      </c>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Chapter_Summary.Biome_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="2" t="inlineStr">
+        <is>
+          <t>사막 도로</t>
+        </is>
+      </c>
+      <c r="B305" s="2" t="inlineStr">
+        <is>
+          <t>Desert Road</t>
+        </is>
+      </c>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Chapter_Summary.Biome_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="2" t="inlineStr">
+        <is>
+          <t>얼어붙은 설원</t>
+        </is>
+      </c>
+      <c r="B306" s="2" t="inlineStr">
+        <is>
+          <t>Frozen Snowfield</t>
+        </is>
+      </c>
+      <c r="C306" s="2" t="inlineStr">
+        <is>
+          <t>Chapter_Summary.Biome_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="2" t="inlineStr">
+        <is>
+          <t>지하 연구소</t>
+        </is>
+      </c>
+      <c r="B307" s="2" t="inlineStr">
+        <is>
+          <t>Underground Lab</t>
+        </is>
+      </c>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Chapter_Summary.Biome_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="2" t="inlineStr">
+        <is>
+          <t>오염 구역</t>
+        </is>
+      </c>
+      <c r="B308" s="2" t="inlineStr">
+        <is>
+          <t>Contaminated Zone</t>
+        </is>
+      </c>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Chapter_Summary.Biome_Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="2" t="inlineStr">
+        <is>
+          <t>무기는 다이아 100 또는 도전 클리어 에서 열립니다</t>
+        </is>
+      </c>
+      <c r="B309" s="2" t="inlineStr">
+        <is>
+          <t>Weapons unlock with 100 gems or a challenge clear</t>
+        </is>
+      </c>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>무기 메뉴가 열렸습니다!</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Weapons unlocked!</t>
+        </is>
+      </c>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Stage 1-2 에서 열립니다</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr">
+        <is>
+          <t>Unlocks at Stage 1-2</t>
+        </is>
+      </c>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>스킨이 열렸습니다!</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr">
+        <is>
+          <t>Skins unlocked!</t>
+        </is>
+      </c>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Stage 4-1 에서 열립니다</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr">
+        <is>
+          <t>Unlocks at Stage 4-1</t>
+        </is>
+      </c>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>다이아 광산이 열렸습니다!</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr">
+        <is>
+          <t>Gem Mine unlocked!</t>
+        </is>
+      </c>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>Stage 6-1 에서 열립니다</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr">
+        <is>
+          <t>Unlocks at Stage 6-1</t>
+        </is>
+      </c>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>보급품이 열렸습니다!</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr">
+        <is>
+          <t>Supplies unlocked!</t>
+        </is>
+      </c>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Stage 10-1 에서 열립니다</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr">
+        <is>
+          <t>Unlocks at Stage 10-1</t>
+        </is>
+      </c>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>보스 던전이 열렸습니다!</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr">
+        <is>
+          <t>Boss Dungeon unlocked!</t>
+        </is>
+      </c>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>큰 푸른 보석</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr">
+        <is>
+          <t>Big Blue Gem</t>
+        </is>
+      </c>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>Mine_Ore_Spec.Name_KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>작은 푸른 보석</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr">
+        <is>
+          <t>Small Blue Gem</t>
+        </is>
+      </c>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>Mine_Ore_Spec.Name_KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>회색 바위</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Gray Rock</t>
+        </is>
+      </c>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>Mine_Ore_Spec.Name_KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
           <t>거대 황금 크리스탈</t>
         </is>
       </c>
-      <c r="B286" s="2" t="inlineStr">
+      <c r="B322" s="2" t="inlineStr">
         <is>
           <t>Huge Gold Crystal</t>
         </is>
       </c>
-      <c r="C286" s="2" t="inlineStr">
+      <c r="C322" s="2" t="inlineStr">
         <is>
           <t>Mine_Ore_Spec.Name_KR</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>S 등급 레이저 건 즉시 지급</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr">
+        <is>
+          <t>Get an S grade Laser Gun now</t>
+        </is>
+      </c>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>리볼버</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr">
+        <is>
+          <t>Revolver</t>
+        </is>
+      </c>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>소드오프 샷건</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr">
+        <is>
+          <t>Sawed-off Shotgun</t>
+        </is>
+      </c>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>우지</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr">
+        <is>
+          <t>Uzi</t>
+        </is>
+      </c>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>상위 리볼버</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr">
+        <is>
+          <t>Elite Revolver</t>
+        </is>
+      </c>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>펌프액션 샷건</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Pump Shotgun</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>돌격소총</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Assault Rifle</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t>매그넘</t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr">
+        <is>
+          <t>Magnum</t>
+        </is>
+      </c>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>전투 샷건</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Combat Shotgun</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>중기관총</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Heavy MG</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>관통 라이플</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Piercing Rifle</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>황금 매그넘</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Golden Magnum</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>드래곤 샷건</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Dragon Shotgun</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>미니건</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr">
+        <is>
+          <t>Minigun</t>
+        </is>
+      </c>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>레일 라이플</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr">
+        <is>
+          <t>Rail Rifle</t>
+        </is>
+      </c>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>레이저 건</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr">
+        <is>
+          <t>Laser Gun</t>
+        </is>
+      </c>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>미사일 런처</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr">
+        <is>
+          <t>Missile Launcher</t>
+        </is>
+      </c>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>플라즈마 레이저</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr">
+        <is>
+          <t>Plasma Laser</t>
+        </is>
+      </c>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>다연장 미사일</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr">
+        <is>
+          <t>Multi Missile</t>
+        </is>
+      </c>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>오메가 레이저</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Omega Laser</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>핵 미사일</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Nuke Missile</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>하이퍼 레이저</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Hyper Laser</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>전술 핵 미사일</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Tactical Nuke</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>퀘이사 레이저</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Quasar Laser</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>반물질 미사일</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Antimatter Missile</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>네뷸라 레이저</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Nebula Laser</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>중력자 미사일</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Graviton Missile</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>노바 레이저</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Nova Laser</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>초신성 미사일</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Supernova Missile</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>보이드 레이저</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Void Laser</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>차원파괴 미사일</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Rift Missile</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>제네시스 레이저</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Genesis Laser</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>아포칼립스 미사일</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Apocalypse Missile</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
         </is>
       </c>
     </row>

--- a/Kachi_Gun/Table/String.xlsx
+++ b/Kachi_Gun/Table/String.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C355"/>
+  <dimension ref="A1:C356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -1746,12 +1746,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>{0}원</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>KRW {0}</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -1763,12 +1763,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -1780,12 +1780,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>희귀</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>영웅</t>
+          <t>희귀</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -1814,12 +1814,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>전설</t>
+          <t>영웅</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>신화</t>
+          <t>전설</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Mythic</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -1848,12 +1848,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>초월</t>
+          <t>신화</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Transcendent</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -1865,12 +1865,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>불멸</t>
+          <t>초월</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Immortal</t>
+          <t>Transcendent</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>보급품 구매</t>
+          <t>불멸</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Buy Supply</t>
+          <t>Immortal</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>공격 +{0}% · 속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
+          <t>보급품 구매</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
+          <t>Buy Supply</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>보유 효과 합계 ({0}/{1})</t>
+          <t>공격 +{0}% · 속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Total owned bonus ({0}/{1})</t>
+          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
+          <t>보유 효과 합계 ({0}/{1})</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
+          <t>Total owned bonus ({0}/{1})</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>챕터 {0}</t>
+          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Ch. {0}</t>
+          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -1967,12 +1967,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>모든 단계 완료</t>
+          <t>챕터 {0}</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>All tiers complete</t>
+          <t>Ch. {0}</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>모든 단계 완료</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>All tiers complete</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2001,12 +2001,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>받기</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>받기</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>배경음</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>효과음</t>
+          <t>배경음</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>진동</t>
+          <t>효과음</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Vibration</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>던전에서는 바꿀 수 없습니다</t>
+          <t>진동</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Can't change during a dungeon</t>
+          <t>Vibration</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>던전에서는 바꿀 수 없습니다</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Can't change during a dungeon</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>저장했습니다 (기기 안)</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Saved (on this device)</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>불러오기 · 구매 복원 · 문의</t>
+          <t>저장했습니다 (기기 안)</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Load · Restore · Contact</t>
+          <t>Saved (on this device)</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>클라우드 저장·결제 복원·문의는 준비 중입니다</t>
+          <t>불러오기 · 구매 복원 · 문의</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Cloud save, restore and contact are coming soon</t>
+          <t>Load · Restore · Contact</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>켜짐</t>
+          <t>클라우드 저장·결제 복원·문의는 준비 중입니다</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Cloud save, restore and contact are coming soon</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>꺼짐</t>
+          <t>켜짐</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>On</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2205,29 +2205,29 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>꺼짐</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>시작</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2239,12 +2239,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>{0}초 안에 좀비 {1}마리를 모두 처치!</t>
+          <t>시작</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Defeat all {1} zombies within {0}s!</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2256,12 +2256,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>화면을 눌러 분대를 직접 움직이면 빨라요</t>
+          <t>{0}초 안에 좀비 {1}마리를 모두 처치!</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Tap the screen to move your squad — it's faster</t>
+          <t>Defeat all {1} zombies within {0}s!</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>보상: 다이아 {0} (챕터당 1번)</t>
+          <t>화면을 눌러 분대를 직접 움직이면 빨라요</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Reward: {0} gems (once per chapter)</t>
+          <t>Tap the screen to move your squad — it's faster</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -2290,12 +2290,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>보상 없음</t>
+          <t>보상: 다이아 {0} (챕터당 1번)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>No reward</t>
+          <t>Reward: {0} gems (once per chapter)</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -2307,12 +2307,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>다이아 광산 {0}단계</t>
+          <t>보상 없음</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Gem Mine Tier {0}</t>
+          <t>No reward</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -2324,12 +2324,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>모든 공격이 1 피해로 고정!</t>
+          <t>다이아 광산 {0}단계</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Every hit deals exactly 1 damage!</t>
+          <t>Gem Mine Tier {0}</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>오늘 티켓</t>
+          <t>모든 공격이 1 피해로 고정!</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Today's tickets</t>
+          <t>Every hit deals exactly 1 damage!</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>{0}초 안에 {1}를 처치!</t>
+          <t>오늘 티켓</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Defeat {1} within {0}s!</t>
+          <t>Today's tickets</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -2375,12 +2375,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>체력</t>
+          <t>{0}초 안에 {1}를 처치!</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Defeat {1} within {0}s!</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>보상: 다이아 {0}</t>
+          <t>체력</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Reward: {0} gems</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>광고 보고</t>
+          <t>보상: 다이아 {0}</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Watch ad</t>
+          <t>Reward: {0} gems</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -2426,12 +2426,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>돌아가기</t>
+          <t>광고 보고</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Watch ad</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -2443,29 +2443,29 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>총알</t>
+          <t>돌아가기</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Ammo</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>리더</t>
+          <t>총알</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>Ammo</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -2477,12 +2477,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>동료 1</t>
+          <t>리더</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Ally 1</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -2494,12 +2494,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>동료 2</t>
+          <t>동료 1</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Ally 2</t>
+          <t>Ally 1</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -2511,12 +2511,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>동료 2</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Ally 2</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -2528,12 +2528,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>강화</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -2545,12 +2545,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>D 등급 총알 획득!</t>
+          <t>강화</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Got D grade ammo!</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>같은 등급 두 개를 끌어다 겹치면 합성!\n장착 칸을 누르면 슬롯 강화 · 남는 총알은 분해 → 다이아</t>
+          <t>D 등급 총알 획득!</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Drag two of the same grade together to merge!\nTap an equip slot to enhance · Salvage spares → gems</t>
+          <t>Got D grade ammo!</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -2579,12 +2579,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>같은 등급 두 개를 끌어다 겹치면 합성!\n장착 칸을 누르면 슬롯 강화 · 남는 총알은 분해 → 다이아</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Drag two of the same grade together to merge!\nTap an equip slot to enhance · Salvage spares → gems</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>총알을 누르면 정보가 나옵니다.\n장착 칸으로 끌어다 놓으면 장착!</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Tap ammo to see its info.\nDrag it onto an equip slot to equip!</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -2613,12 +2613,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>{0}발</t>
+          <t>총알을 누르면 정보가 나옵니다.\n장착 칸으로 끌어다 놓으면 장착!</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>{0} pellets</t>
+          <t>Tap ammo to see its info.\nDrag it onto an equip slot to equip!</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>{0}마리 관통</t>
+          <t>{0}발</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>pierces {0}</t>
+          <t>{0} pellets</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -2647,12 +2647,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>범위 {0}</t>
+          <t>{0}마리 관통</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>radius {0}</t>
+          <t>pierces {0}</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>일직선 전부</t>
+          <t>범위 {0}</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>hits the whole line</t>
+          <t>radius {0}</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>공격력 {0} · 연사 {1}초</t>
+          <t>일직선 전부</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>ATK {0} · fires every {1}s</t>
+          <t>hits the whole line</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>넘친 공속 → 공격 x{0}</t>
+          <t>공격력 {0} · 연사 {1}초</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>Excess speed → ATK x{0}</t>
+          <t>ATK {0} · fires every {1}s</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>(칸 +{0}, 이 등급은 +{1}까지)</t>
+          <t>넘친 공속 → 공격 x{0}</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>(slot +{0}, this grade caps at +{1})</t>
+          <t>Excess speed → ATK x{0}</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>최대 +{0}</t>
+          <t>(칸 +{0}, 이 등급은 +{1}까지)</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>max +{0}</t>
+          <t>(slot +{0}, this grade caps at +{1})</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>슬롯 강화 +{0}</t>
+          <t>최대 +{0}</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Slot +{0}</t>
+          <t>max +{0}</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>공격 +{0}% · 속도 +{1}% · 보스 +{2}%</t>
+          <t>슬롯 강화 +{0}</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Boss +{2}%</t>
+          <t>Slot +{0}</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>분해</t>
+          <t>공격 +{0}% · 속도 +{1}% · 보스 +{2}%</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Salvage</t>
+          <t>ATK +{0}% · SPD +{1}% · Boss +{2}%</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>해제</t>
+          <t>분해</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Unequip</t>
+          <t>Salvage</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>{0} 을(를) 분해할까요?</t>
+          <t>해제</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Salvage {0}?</t>
+          <t>Unequip</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>슬롯 강화</t>
+          <t>{0} 을(를) 분해할까요?</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Slot Enhance</t>
+          <t>Salvage {0}?</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>성공 확률 {0}%</t>
+          <t>슬롯 강화</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Success rate {0}%</t>
+          <t>Slot Enhance</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>공격속도 +{0}% · 보스 피해 +{1}%</t>
+          <t>성공 확률 {0}%</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>SPD +{0}% · Boss DMG +{1}%</t>
+          <t>Success rate {0}%</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -2885,12 +2885,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>강화 성공!</t>
+          <t>공격속도 +{0}% · 보스 피해 +{1}%</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Enhanced!</t>
+          <t>SPD +{0}% · Boss DMG +{1}%</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>강화 실패… (재료만 사라짐)</t>
+          <t>강화 성공!</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Enhance failed… (materials lost)</t>
+          <t>Enhanced!</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>합성!</t>
+          <t>강화 실패… (재료만 사라짐)</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Merged!</t>
+          <t>Enhance failed… (materials lost)</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>장착 중인 총알은 해제한 뒤 합성할 수 있습니다</t>
+          <t>합성!</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Unequip ammo before merging it</t>
+          <t>Merged!</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -2953,29 +2953,29 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>기본 카피</t>
+          <t>장착 중인 총알은 해제한 뒤 합성할 수 있습니다</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Classic Capy</t>
+          <t>Unequip ammo before merging it</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>밀짚모자</t>
+          <t>기본 카피</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Straw Hat</t>
+          <t>Classic Capy</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>천사 날개</t>
+          <t>밀짚모자</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Angel Wings</t>
+          <t>Straw Hat</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -3004,12 +3004,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>새싹</t>
+          <t>천사 날개</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Sprout</t>
+          <t>Angel Wings</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>꿀꿀 돼지</t>
+          <t>새싹</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Piggy</t>
+          <t>Sprout</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>악어 잠옷</t>
+          <t>꿀꿀 돼지</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Croc Pajamas</t>
+          <t>Piggy</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>원시인</t>
+          <t>악어 잠옷</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Caveman</t>
+          <t>Croc Pajamas</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>검은 두건</t>
+          <t>원시인</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Black Hood</t>
+          <t>Caveman</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>그림자 망토</t>
+          <t>검은 두건</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Shadow Cloak</t>
+          <t>Black Hood</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>공룡 잠옷</t>
+          <t>그림자 망토</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Dino Pajamas</t>
+          <t>Shadow Cloak</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -3123,12 +3123,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>모험가 배낭</t>
+          <t>공룡 잠옷</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Explorer's Pack</t>
+          <t>Dino Pajamas</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -3140,12 +3140,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>박쥐 날개</t>
+          <t>모험가 배낭</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Bat Wings</t>
+          <t>Explorer's Pack</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>멜빵바지</t>
+          <t>박쥐 날개</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Overalls</t>
+          <t>Bat Wings</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -3174,12 +3174,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>꼬꼬 잠옷</t>
+          <t>멜빵바지</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Chicken Pajamas</t>
+          <t>Overalls</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>빨간 망토</t>
+          <t>꼬꼬 잠옷</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Red Cape</t>
+          <t>Chicken Pajamas</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>상어 잠옷</t>
+          <t>빨간 망토</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Shark Pajamas</t>
+          <t>Red Cape</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -3225,12 +3225,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>줄무늬 고양이</t>
+          <t>상어 잠옷</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Tabby Cat</t>
+          <t>Shark Pajamas</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>해적 선장</t>
+          <t>줄무늬 고양이</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Pirate Captain</t>
+          <t>Tabby Cat</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -3259,29 +3259,29 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>기본탄_D</t>
+          <t>해적 선장</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_D</t>
+          <t>Pirate Captain</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>산탄_D</t>
+          <t>기본탄_D</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_D</t>
+          <t>Basic Round_D</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>속사탄_D</t>
+          <t>산탄_D</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_D</t>
+          <t>Buckshot_D</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>기본탄_C</t>
+          <t>속사탄_D</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_C</t>
+          <t>Rapid Round_D</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>산탄_C</t>
+          <t>기본탄_C</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_C</t>
+          <t>Basic Round_C</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -3344,12 +3344,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>관통탄_C</t>
+          <t>산탄_C</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_C</t>
+          <t>Buckshot_C</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>기본탄_B</t>
+          <t>관통탄_C</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_B</t>
+          <t>Piercing Round_C</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>산탄_B</t>
+          <t>기본탄_B</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_B</t>
+          <t>Basic Round_B</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>속사탄_B</t>
+          <t>산탄_B</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_B</t>
+          <t>Buckshot_B</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
@@ -3412,12 +3412,12 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>관통탄_B</t>
+          <t>속사탄_B</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_B</t>
+          <t>Rapid Round_B</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>기본탄_A</t>
+          <t>관통탄_B</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_A</t>
+          <t>Piercing Round_B</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
@@ -3446,12 +3446,12 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>산탄_A</t>
+          <t>기본탄_A</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_A</t>
+          <t>Basic Round_A</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
@@ -3463,12 +3463,12 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>속사탄_A</t>
+          <t>산탄_A</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_A</t>
+          <t>Buckshot_A</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>관통탄_A</t>
+          <t>속사탄_A</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_A</t>
+          <t>Rapid Round_A</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
@@ -3497,12 +3497,12 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>기본탄_S</t>
+          <t>관통탄_A</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_S</t>
+          <t>Piercing Round_A</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>산탄_S</t>
+          <t>기본탄_S</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_S</t>
+          <t>Basic Round_S</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>속사탄_S</t>
+          <t>산탄_S</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_S</t>
+          <t>Buckshot_S</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>관통탄_S</t>
+          <t>속사탄_S</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_S</t>
+          <t>Rapid Round_S</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_S</t>
+          <t>관통탄_S</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_S</t>
+          <t>Piercing Round_S</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_S</t>
+          <t>레이저탄_S</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Missile_S</t>
+          <t>Laser Round_S</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SS</t>
+          <t>미사일탄_S</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SS</t>
+          <t>Missile_S</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>산탄_SS</t>
+          <t>기본탄_SS</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SS</t>
+          <t>Basic Round_SS</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SS</t>
+          <t>산탄_SS</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SS</t>
+          <t>Buckshot_SS</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SS</t>
+          <t>속사탄_SS</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SS</t>
+          <t>Rapid Round_SS</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SS</t>
+          <t>관통탄_SS</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SS</t>
+          <t>Piercing Round_SS</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SS</t>
+          <t>레이저탄_SS</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Missile_SS</t>
+          <t>Laser Round_SS</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SSS</t>
+          <t>미사일탄_SS</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SSS</t>
+          <t>Missile_SS</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>산탄_SSS</t>
+          <t>기본탄_SSS</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SSS</t>
+          <t>Basic Round_SSS</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SSS</t>
+          <t>산탄_SSS</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SSS</t>
+          <t>Buckshot_SSS</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SSS</t>
+          <t>속사탄_SSS</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SSS</t>
+          <t>Rapid Round_SSS</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SSS</t>
+          <t>관통탄_SSS</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SSS</t>
+          <t>Piercing Round_SSS</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SSS</t>
+          <t>레이저탄_SSS</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Missile_SSS</t>
+          <t>Laser Round_SSS</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>기본탄_R</t>
+          <t>미사일탄_SSS</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_R</t>
+          <t>Missile_SSS</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>산탄_R</t>
+          <t>기본탄_R</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_R</t>
+          <t>Basic Round_R</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>속사탄_R</t>
+          <t>산탄_R</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_R</t>
+          <t>Buckshot_R</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>관통탄_R</t>
+          <t>속사탄_R</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_R</t>
+          <t>Rapid Round_R</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_R</t>
+          <t>관통탄_R</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_R</t>
+          <t>Piercing Round_R</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_R</t>
+          <t>레이저탄_R</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Missile_R</t>
+          <t>Laser Round_R</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SR</t>
+          <t>미사일탄_R</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SR</t>
+          <t>Missile_R</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>산탄_SR</t>
+          <t>기본탄_SR</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SR</t>
+          <t>Basic Round_SR</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SR</t>
+          <t>산탄_SR</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SR</t>
+          <t>Buckshot_SR</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SR</t>
+          <t>속사탄_SR</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SR</t>
+          <t>Rapid Round_SR</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SR</t>
+          <t>관통탄_SR</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SR</t>
+          <t>Piercing Round_SR</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SR</t>
+          <t>레이저탄_SR</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Missile_SR</t>
+          <t>Laser Round_SR</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SSR</t>
+          <t>미사일탄_SR</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SSR</t>
+          <t>Missile_SR</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>산탄_SSR</t>
+          <t>기본탄_SSR</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SSR</t>
+          <t>Basic Round_SSR</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SSR</t>
+          <t>산탄_SSR</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SSR</t>
+          <t>Buckshot_SSR</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SSR</t>
+          <t>속사탄_SSR</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SSR</t>
+          <t>Rapid Round_SSR</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SSR</t>
+          <t>관통탄_SSR</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SSR</t>
+          <t>Piercing Round_SSR</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SSR</t>
+          <t>레이저탄_SSR</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Missile_SSR</t>
+          <t>Laser Round_SSR</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>기본탄_U</t>
+          <t>미사일탄_SSR</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_U</t>
+          <t>Missile_SSR</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>산탄_U</t>
+          <t>기본탄_U</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_U</t>
+          <t>Basic Round_U</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>속사탄_U</t>
+          <t>산탄_U</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_U</t>
+          <t>Buckshot_U</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>관통탄_U</t>
+          <t>속사탄_U</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_U</t>
+          <t>Rapid Round_U</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_U</t>
+          <t>관통탄_U</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_U</t>
+          <t>Piercing Round_U</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_U</t>
+          <t>레이저탄_U</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Missile_U</t>
+          <t>Laser Round_U</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SU</t>
+          <t>미사일탄_U</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SU</t>
+          <t>Missile_U</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>산탄_SU</t>
+          <t>기본탄_SU</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SU</t>
+          <t>Basic Round_SU</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -4245,12 +4245,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SU</t>
+          <t>산탄_SU</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SU</t>
+          <t>Buckshot_SU</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SU</t>
+          <t>속사탄_SU</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SU</t>
+          <t>Rapid Round_SU</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SU</t>
+          <t>관통탄_SU</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SU</t>
+          <t>Piercing Round_SU</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SU</t>
+          <t>레이저탄_SU</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Missile_SU</t>
+          <t>Laser Round_SU</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SSU</t>
+          <t>미사일탄_SU</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SSU</t>
+          <t>Missile_SU</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>산탄_SSU</t>
+          <t>기본탄_SSU</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SSU</t>
+          <t>Basic Round_SSU</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -4347,12 +4347,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SSU</t>
+          <t>산탄_SSU</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SSU</t>
+          <t>Buckshot_SSU</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -4364,12 +4364,12 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SSU</t>
+          <t>속사탄_SSU</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SSU</t>
+          <t>Rapid Round_SSU</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SSU</t>
+          <t>관통탄_SSU</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SSU</t>
+          <t>Piercing Round_SSU</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SSU</t>
+          <t>레이저탄_SSU</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Missile_SSU</t>
+          <t>Laser Round_SSU</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -4415,29 +4415,29 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>기어오는 좀비</t>
+          <t>미사일탄_SSU</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Crawler</t>
+          <t>Missile_SSU</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>칼 좀비</t>
+          <t>기어오는 좀비</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Knife Zombie</t>
+          <t>Crawler</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>좀비</t>
+          <t>칼 좀비</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Zombie</t>
+          <t>Knife Zombie</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>모자 좀비</t>
+          <t>좀비</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Hat Zombie</t>
+          <t>Zombie</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>양동이 좀비</t>
+          <t>모자 좀비</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Bucket Zombie</t>
+          <t>Hat Zombie</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>갑옷 좀비</t>
+          <t>양동이 좀비</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Armored Zombie</t>
+          <t>Bucket Zombie</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>방망이 좀비</t>
+          <t>갑옷 좀비</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Bat Zombie</t>
+          <t>Armored Zombie</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>농부 좀비</t>
+          <t>방망이 좀비</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Farmer Zombie</t>
+          <t>Bat Zombie</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>미라</t>
+          <t>농부 좀비</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Mummy</t>
+          <t>Farmer Zombie</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>뚱보 좀비</t>
+          <t>미라</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Fat Zombie</t>
+          <t>Mummy</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
@@ -4585,12 +4585,12 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>사신 좀비</t>
+          <t>뚱보 좀비</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Reaper Zombie</t>
+          <t>Fat Zombie</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>변이 오우거</t>
+          <t>사신 좀비</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Mutant Ogre</t>
+          <t>Reaper Zombie</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
@@ -4619,29 +4619,29 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>비상 건빵</t>
+          <t>변이 오우거</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Emergency Crackers</t>
+          <t>Mutant Ogre</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>통조림 캔</t>
+          <t>비상 건빵</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Canned Food</t>
+          <t>Emergency Crackers</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>정수 필터</t>
+          <t>통조림 캔</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Water Filter</t>
+          <t>Canned Food</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>야전 반합</t>
+          <t>정수 필터</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Mess Kit</t>
+          <t>Water Filter</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
@@ -4687,12 +4687,12 @@
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>에너지 바</t>
+          <t>야전 반합</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Energy Bar</t>
+          <t>Mess Kit</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
@@ -4704,12 +4704,12 @@
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>구급 상자</t>
+          <t>에너지 바</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Energy Bar</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
@@ -4721,12 +4721,12 @@
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>아드레날린 주사</t>
+          <t>구급 상자</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>Adrenaline Shot</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>군용 무전기</t>
+          <t>아드레날린 주사</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Field Radio</t>
+          <t>Adrenaline Shot</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>야간 투시경</t>
+          <t>군용 무전기</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Night Vision</t>
+          <t>Field Radio</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>방탄 조끼</t>
+          <t>야간 투시경</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Bulletproof Vest</t>
+          <t>Night Vision</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>전술 탄띠</t>
+          <t>방탄 조끼</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Tactical Bandolier</t>
+          <t>Bulletproof Vest</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
@@ -4806,12 +4806,12 @@
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>고농축 스팀팩</t>
+          <t>전술 탄띠</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Mega Stimpack</t>
+          <t>Tactical Bandolier</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>열화우라늄 탄심</t>
+          <t>고농축 스팀팩</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>DU Core</t>
+          <t>Mega Stimpack</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>냉각 모듈</t>
+          <t>열화우라늄 탄심</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>Cooling Module</t>
+          <t>DU Core</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>플라즈마 배터리</t>
+          <t>냉각 모듈</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Plasma Battery</t>
+          <t>Cooling Module</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>양자 증폭기</t>
+          <t>플라즈마 배터리</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Quantum Amplifier</t>
+          <t>Plasma Battery</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>중력 제어 코어</t>
+          <t>양자 증폭기</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Gravity Core</t>
+          <t>Quantum Amplifier</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>나노 수복 혈청</t>
+          <t>중력 제어 코어</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Nano Serum</t>
+          <t>Gravity Core</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>바이오 리액터</t>
+          <t>나노 수복 혈청</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Bio Reactor</t>
+          <t>Nano Serum</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>초전도 코일</t>
+          <t>바이오 리액터</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Superconductor Coil</t>
+          <t>Bio Reactor</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>암흑물질 셀</t>
+          <t>초전도 코일</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Dark Matter Cell</t>
+          <t>Superconductor Coil</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>차원 도약 엔진</t>
+          <t>암흑물질 셀</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Warp Engine</t>
+          <t>Dark Matter Cell</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>항성 에너지 핵</t>
+          <t>차원 도약 엔진</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Stellar Core</t>
+          <t>Warp Engine</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>영구기관 모듈</t>
+          <t>항성 에너지 핵</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Perpetual Engine</t>
+          <t>Stellar Core</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>카피바라의 성배</t>
+          <t>영구기관 모듈</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Capybara Grail</t>
+          <t>Perpetual Engine</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -5044,46 +5044,46 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>태초</t>
+          <t>카피바라의 성배</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Primordial</t>
+          <t>Capybara Grail</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Grade</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>좀비 처치하기</t>
+          <t>태초</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Defeat zombies</t>
+          <t>Primordial</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Supply_Collection.Grade</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>스테이지 클리어하기</t>
+          <t>좀비 처치하기</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Clear stages</t>
+          <t>Defeat zombies</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>광산 플레이하기</t>
+          <t>스테이지 클리어하기</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Play the mine</t>
+          <t>Clear stages</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>보스 처치하기</t>
+          <t>광산 플레이하기</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Defeat bosses</t>
+          <t>Play the mine</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>총알 합성하기</t>
+          <t>보스 처치하기</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Merge ammo</t>
+          <t>Defeat bosses</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
@@ -5146,63 +5146,63 @@
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>공격력 x2 (5분)</t>
+          <t>총알 합성하기</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Attack x2 (5 min)</t>
+          <t>Merge ammo</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>광고 1편 · 연속 시청 시 시간 누적</t>
+          <t>공격력 x2 (5분)</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>1 ad · time stacks when watched again</t>
+          <t>Attack x2 (5 min)</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>돈 획득량 x2 (5분)</t>
+          <t>광고 1편 · 연속 시청 시 시간 누적</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>Gold x2 (5 min)</t>
+          <t>1 ad · time stacks when watched again</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>강제 광고 제거</t>
+          <t>돈 획득량 x2 (5분)</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Remove Forced Ads</t>
+          <t>Gold x2 (5 min)</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
@@ -5214,709 +5214,709 @@
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>자동 전면 광고 제거 + 돼지저금통</t>
+          <t>모든 광고 제거</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>No more forced ads + piggy bank</t>
+          <t>Remove All Ads</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>모든 광고 제거</t>
+          <t>보상형 광고도 바로 보상</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Remove All Ads</t>
+          <t>Rewards without watching ads</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>보상형 광고도 바로 보상</t>
+          <t>자동강화 패키지</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Rewards without watching ads</t>
+          <t>Auto Upgrade Pack</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>자동강화 패키지</t>
+          <t>하단 강화 자동 + 다이아 500</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Auto Upgrade Pack</t>
+          <t>Upgrades buy themselves + 500 gems</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>하단 강화 자동 + 다이아 500</t>
+          <t>다이아 한 줌 (500)</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Upgrades buy themselves + 500 gems</t>
+          <t>Handful of Gems (500)</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>영구 3배 버프</t>
+          <t>다이아 500개 즉시 획득</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Permanent x3 Buff</t>
+          <t>Get 500 gems now</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
+          <t>다이아 주머니 (1,800)</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Permanent x3 attack &amp; gold + 1,000 gems</t>
+          <t>Pouch of Gems (1,800)</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>광산 티켓 확장</t>
+          <t>다이아 1,800개 즉시 획득</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Mine Ticket Pack</t>
+          <t>Get 1,800 gems now</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
+          <t>다이아 상자 (4,200)</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Daily mine tickets 2 → 6 + 500 gems</t>
+          <t>Chest of Gems (4,200)</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>핫딜 레이저 총알</t>
+          <t>다이아 4,200개 즉시 획득</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Hot Deal: Laser Ammo</t>
+          <t>Get 4,200 gems now</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_S 즉시 지급</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Get a Laser Round_S now</t>
+          <t>Free Gems</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>다이아 한 줌 (500)</t>
+          <t>광고 1편 · 다이아 40 · 하루 3번</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>Handful of Gems (500)</t>
+          <t>1 ad · 40 gems · 3 times a day</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>다이아 500개 즉시 획득</t>
+          <t>폐허 숲길</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Get 500 gems now</t>
+          <t>Ruined Forest Trail</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>다이아 주머니 (1,800)</t>
+          <t>오염된 해안</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Pouch of Gems (1,800)</t>
+          <t>Polluted Coast</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>다이아 1,800개 즉시 획득</t>
+          <t>사막 도로</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Get 1,800 gems now</t>
+          <t>Desert Road</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>다이아 상자 (4,200)</t>
+          <t>얼어붙은 설원</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Chest of Gems (4,200)</t>
+          <t>Frozen Snowfield</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>다이아 4,200개 즉시 획득</t>
+          <t>지하 연구소</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Get 4,200 gems now</t>
+          <t>Underground Lab</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>30분 방치 골드 상자</t>
+          <t>오염 구역</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>30-min Gold Chest</t>
+          <t>Contaminated Zone</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>현재 스테이지 기준 600마리 처치 골드</t>
+          <t>무기는 다이아 100 또는 도전 클리어 에서 열립니다</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Gold of 600 zombies at your current stage</t>
+          <t>Weapons unlock with 100 gems or a challenge clear</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>무기 메뉴가 열렸습니다!</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Free Gems</t>
+          <t>Weapons unlocked!</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>광고 1편 · 다이아 40 · 하루 3번</t>
+          <t>Stage 1-2 에서 열립니다</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>1 ad · 40 gems · 3 times a day</t>
+          <t>Unlocks at Stage 1-2</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>폐허 숲길</t>
+          <t>스킨이 열렸습니다!</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Ruined Forest Trail</t>
+          <t>Skins unlocked!</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>오염된 해안</t>
+          <t>Stage 4-1 에서 열립니다</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Polluted Coast</t>
+          <t>Unlocks at Stage 4-1</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>사막 도로</t>
+          <t>다이아 광산이 열렸습니다!</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Desert Road</t>
+          <t>Gem Mine unlocked!</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>얼어붙은 설원</t>
+          <t>Stage 6-1 에서 열립니다</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Frozen Snowfield</t>
+          <t>Unlocks at Stage 6-1</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>지하 연구소</t>
+          <t>보급품이 열렸습니다!</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Underground Lab</t>
+          <t>Supplies unlocked!</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>오염 구역</t>
+          <t>Stage 10-1 에서 열립니다</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Contaminated Zone</t>
+          <t>Unlocks at Stage 10-1</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>무기는 다이아 100 또는 도전 클리어 에서 열립니다</t>
+          <t>보스 던전이 열렸습니다!</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Weapons unlock with 100 gems or a challenge clear</t>
+          <t>Boss Dungeon unlocked!</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>무기 메뉴가 열렸습니다!</t>
+          <t>큰 푸른 보석</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Weapons unlocked!</t>
+          <t>Big Blue Gem</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>Stage 1-2 에서 열립니다</t>
+          <t>작은 푸른 보석</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 1-2</t>
+          <t>Small Blue Gem</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>스킨이 열렸습니다!</t>
+          <t>회색 바위</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Skins unlocked!</t>
+          <t>Gray Rock</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>Stage 4-1 에서 열립니다</t>
+          <t>거대 황금 크리스탈</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 4-1</t>
+          <t>Huge Gold Crystal</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>다이아 광산이 열렸습니다!</t>
+          <t>강제 광고 제거</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Gem Mine unlocked!</t>
+          <t>Remove Forced Ads</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>Stage 6-1 에서 열립니다</t>
+          <t>자동 전면 광고 제거 + 돼지저금통</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 6-1</t>
+          <t>No more forced ads + piggy bank</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>보급품이 열렸습니다!</t>
+          <t>영구 3배 버프</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Supplies unlocked!</t>
+          <t>Permanent x3 Buff</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>Stage 10-1 에서 열립니다</t>
+          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 10-1</t>
+          <t>Permanent x3 attack &amp; gold + 1,000 gems</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>보스 던전이 열렸습니다!</t>
+          <t>광산 티켓 확장</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Boss Dungeon unlocked!</t>
+          <t>Mine Ticket Pack</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>큰 푸른 보석</t>
+          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Big Blue Gem</t>
+          <t>Daily mine tickets 2 → 6 + 500 gems</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>작은 푸른 보석</t>
+          <t>핫딜 레이저 총알</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Small Blue Gem</t>
+          <t>Hot Deal: Laser Ammo</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>회색 바위</t>
+          <t>레이저탄_S 즉시 지급</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Gray Rock</t>
+          <t>Get a Laser Round_S now</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>거대 황금 크리스탈</t>
+          <t>30분 방치 골드 상자</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>Huge Gold Crystal</t>
+          <t>30-min Gold Chest</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>S 등급 레이저 건 즉시 지급</t>
+          <t>현재 스테이지 기준 600마리 처치 골드</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Get an S grade Laser Gun now</t>
+          <t>Gold of 600 zombies at your current stage</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
@@ -5928,29 +5928,29 @@
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>리볼버</t>
+          <t>S 등급 레이저 건 즉시 지급</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Revolver</t>
+          <t>Get an S grade Laser Gun now</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>소드오프 샷건</t>
+          <t>리볼버</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Sawed-off Shotgun</t>
+          <t>Revolver</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
@@ -5962,12 +5962,12 @@
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>우지</t>
+          <t>소드오프 샷건</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Uzi</t>
+          <t>Sawed-off Shotgun</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>상위 리볼버</t>
+          <t>우지</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Elite Revolver</t>
+          <t>Uzi</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>펌프액션 샷건</t>
+          <t>상위 리볼버</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Pump Shotgun</t>
+          <t>Elite Revolver</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>돌격소총</t>
+          <t>펌프액션 샷건</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>Pump Shotgun</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>매그넘</t>
+          <t>돌격소총</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Magnum</t>
+          <t>Assault Rifle</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
@@ -6047,12 +6047,12 @@
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>전투 샷건</t>
+          <t>매그넘</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Combat Shotgun</t>
+          <t>Magnum</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
@@ -6064,12 +6064,12 @@
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>중기관총</t>
+          <t>전투 샷건</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Heavy MG</t>
+          <t>Combat Shotgun</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
@@ -6081,12 +6081,12 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>관통 라이플</t>
+          <t>중기관총</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Piercing Rifle</t>
+          <t>Heavy MG</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
@@ -6098,12 +6098,12 @@
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>황금 매그넘</t>
+          <t>관통 라이플</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Golden Magnum</t>
+          <t>Piercing Rifle</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>드래곤 샷건</t>
+          <t>황금 매그넘</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Dragon Shotgun</t>
+          <t>Golden Magnum</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
@@ -6132,12 +6132,12 @@
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>미니건</t>
+          <t>드래곤 샷건</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Minigun</t>
+          <t>Dragon Shotgun</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>레일 라이플</t>
+          <t>미니건</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Rail Rifle</t>
+          <t>Minigun</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>레이저 건</t>
+          <t>레일 라이플</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Laser Gun</t>
+          <t>Rail Rifle</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>미사일 런처</t>
+          <t>레이저 건</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Missile Launcher</t>
+          <t>Laser Gun</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>플라즈마 레이저</t>
+          <t>미사일 런처</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Plasma Laser</t>
+          <t>Missile Launcher</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>다연장 미사일</t>
+          <t>플라즈마 레이저</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Multi Missile</t>
+          <t>Plasma Laser</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>오메가 레이저</t>
+          <t>다연장 미사일</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Omega Laser</t>
+          <t>Multi Missile</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>핵 미사일</t>
+          <t>오메가 레이저</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Nuke Missile</t>
+          <t>Omega Laser</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>하이퍼 레이저</t>
+          <t>핵 미사일</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Hyper Laser</t>
+          <t>Nuke Missile</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>전술 핵 미사일</t>
+          <t>하이퍼 레이저</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Tactical Nuke</t>
+          <t>Hyper Laser</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -6302,12 +6302,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>퀘이사 레이저</t>
+          <t>전술 핵 미사일</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Quasar Laser</t>
+          <t>Tactical Nuke</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>반물질 미사일</t>
+          <t>퀘이사 레이저</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Antimatter Missile</t>
+          <t>Quasar Laser</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>네뷸라 레이저</t>
+          <t>반물질 미사일</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Nebula Laser</t>
+          <t>Antimatter Missile</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>중력자 미사일</t>
+          <t>네뷸라 레이저</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Graviton Missile</t>
+          <t>Nebula Laser</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>노바 레이저</t>
+          <t>중력자 미사일</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Nova Laser</t>
+          <t>Graviton Missile</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>초신성 미사일</t>
+          <t>노바 레이저</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Supernova Missile</t>
+          <t>Nova Laser</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -6404,12 +6404,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>보이드 레이저</t>
+          <t>초신성 미사일</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Void Laser</t>
+          <t>Supernova Missile</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>차원파괴 미사일</t>
+          <t>보이드 레이저</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Rift Missile</t>
+          <t>Void Laser</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>제네시스 레이저</t>
+          <t>차원파괴 미사일</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Genesis Laser</t>
+          <t>Rift Missile</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -6455,15 +6455,32 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
+          <t>제네시스 레이저</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Genesis Laser</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
           <t>아포칼립스 미사일</t>
         </is>
       </c>
-      <c r="B355" s="2" t="inlineStr">
+      <c r="B356" s="2" t="inlineStr">
         <is>
           <t>Apocalypse Missile</t>
         </is>
       </c>
-      <c r="C355" s="2" t="inlineStr">
+      <c r="C356" s="2" t="inlineStr">
         <is>
           <t>(지금은 안 씀) Weapon_Master.Name</t>
         </is>

--- a/Kachi_Gun/Table/String.xlsx
+++ b/Kachi_Gun/Table/String.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C356"/>
+  <dimension ref="A1:C371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -471,12 +471,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>결제는 준비 중입니다</t>
+          <t>광고를 불러오는 중입니다. 잠시 뒤 다시 눌러 주세요</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Purchases are coming soon</t>
+          <t>Loading the ad. Please tap again in a moment.</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -488,352 +488,352 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>{0}초</t>
+          <t>광고를 띄우지 못했습니다. 잠시 뒤 다시 해 주세요</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>{0}s</t>
+          <t>Couldn't show the ad. Please try again later.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Core/Num.cs</t>
+          <t>Core/AdService.cs</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>단발</t>
+          <t>{0} 구매 완료!</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>{0} purchased!</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Core/Tables.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>산탄</t>
+          <t>결제는 준비 중입니다</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Shotgun</t>
+          <t>Purchases are coming soon</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Core/Tables.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>속사</t>
+          <t>이미 가지고 있습니다</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Rapid</t>
+          <t>Already owned</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Core/Tables.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>관통</t>
+          <t>스토어에 연결하는 중입니다. 잠시 뒤 다시 눌러 주세요</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Pierce</t>
+          <t>Connecting to the store. Please tap again in a moment.</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Core/Tables.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>레이저</t>
+          <t>[테스트] 가짜 결제 {0} — 살까요?</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Laser</t>
+          <t>[Test] Fake purchase {0} — buy?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Core/Tables.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>미사일</t>
+          <t>구매</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Missile</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Core/Tables.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>보스 실패! 강화 후 다시 도전하세요</t>
+          <t>결제 승인을 기다리는 중입니다</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Boss failed! Upgrade and try again</t>
+          <t>Waiting for payment approval</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>아직 보스를 만날 때가 아닙니다</t>
+          <t>결제를 확인하지 못했습니다</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>It's not time to face the boss yet</t>
+          <t>Couldn't verify the purchase</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>보스 등장!</t>
+          <t>{0} 구매 기록을 되살렸습니다</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Boss incoming!</t>
+          <t>Restored your purchase: {0}</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>아직 열리지 않았습니다</t>
+          <t>결제를 취소했습니다</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Not unlocked yet</t>
+          <t>Purchase canceled</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>다이아가 부족합니다</t>
+          <t>앞의 결제를 처리하는 중입니다</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Not enough gems</t>
+          <t>A previous purchase is still processing</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>인벤토리가 가득 찼습니다</t>
+          <t>결제하지 못했습니다</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Inventory is full</t>
+          <t>Purchase failed</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Iap.cs</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>최고 등급입니다</t>
+          <t>{0}초</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Already the highest grade</t>
+          <t>{0}s</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Num.cs</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>총알을 장착한 칸만 강화할 수 있습니다</t>
+          <t>단발</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Only slots with ammo equipped can be enhanced</t>
+          <t>Single</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Tables.cs</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>최고 강화입니다</t>
+          <t>산탄</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Already max enhancement</t>
+          <t>Shotgun</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Tables.cs</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>{0} 등급 총알은 +{1} 까지 — 더 높은 등급을 장착하세요</t>
+          <t>속사</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>{0} grade ammo caps at +{1} — equip a higher grade</t>
+          <t>Rapid</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Tables.cs</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>골드가 부족합니다</t>
+          <t>관통</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Not enough gold</t>
+          <t>Pierce</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Tables.cs</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>이미 가진 보급품입니다</t>
+          <t>레이저</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>You already own this supply</t>
+          <t>Laser</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Tables.cs</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>챕터 {0} 에서 열립니다</t>
+          <t>미사일</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at chapter {0}</t>
+          <t>Missile</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Game/GameManager.cs</t>
+          <t>Core/Tables.cs</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>골드</t>
+          <t>보스 실패! 강화 후 다시 도전하세요</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Boss failed! Upgrade and try again</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>최소 1개의 총알을 장착해야 합니다</t>
+          <t>아직 보스를 만날 때가 아닙니다</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>You must equip at least 1 ammo</t>
+          <t>It's not time to face the boss yet</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -862,12 +862,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>빈 칸에만 놓을 수 있습니다</t>
+          <t>보스 등장!</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Can only be placed in an empty slot</t>
+          <t>Boss incoming!</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>{0}초 뒤에 다시 볼 수 있습니다</t>
+          <t>자동강화 켬</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Available again in {0}s</t>
+          <t>Auto upgrade ON</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>다이아</t>
+          <t>자동강화 끔</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Gems</t>
+          <t>Auto upgrade OFF</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>모든 단계를 끝냈습니다</t>
+          <t>아직 열리지 않았습니다</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>All tiers completed</t>
+          <t>Not unlocked yet</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>아직 달성하지 못했습니다</t>
+          <t>다이아가 부족합니다</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Not achieved yet</t>
+          <t>Not enough gems</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>오늘은 다 받았습니다 (내일 다시)</t>
+          <t>인벤토리가 가득 찼습니다</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>All claimed today (come back tomorrow)</t>
+          <t>Inventory is full</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>다음 챕터에서 새 도전이 열립니다</t>
+          <t>최고 등급입니다</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>A new challenge opens next chapter</t>
+          <t>Already the highest grade</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -981,12 +981,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>도전 {0} — 모두 처치!</t>
+          <t>총알을 장착한 칸만 강화할 수 있습니다</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Challenge {0} — defeat them all!</t>
+          <t>Only slots with ammo equipped can be enhanced</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -998,12 +998,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>오늘 티켓을 다 썼습니다</t>
+          <t>최고 강화입니다</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>No tickets left today</t>
+          <t>Already max enhancement</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -1015,12 +1015,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>다이아 광산</t>
+          <t>{0} 등급 총알은 +{1} 까지 — 더 높은 등급을 장착하세요</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Gem Mine</t>
+          <t>{0} grade ammo caps at +{1} — equip a higher grade</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1032,12 +1032,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>보스 던전 Lv.{0}</t>
+          <t>골드가 부족합니다</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Boss Dungeon Lv.{0}</t>
+          <t>Not enough gold</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -1049,12 +1049,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>도전 {0} 성공!</t>
+          <t>이미 가진 보급품입니다</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Challenge {0} cleared!</t>
+          <t>You already own this supply</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>시간 초과</t>
+          <t>챕터 {0} 에서 열립니다</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Time's up</t>
+          <t>Unlocks at chapter {0}</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -1083,12 +1083,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>채굴 끝!</t>
+          <t>골드</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Mining done!</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -1100,12 +1100,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>보스 처치!</t>
+          <t>최소 1개의 총알을 장착해야 합니다</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Boss defeated!</t>
+          <t>You must equip at least 1 ammo</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -1117,267 +1117,267 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>절전모드</t>
+          <t>빈 칸에만 놓을 수 있습니다</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Eco</t>
+          <t>Can only be placed in an empty slot</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>상점</t>
+          <t>{0}초 뒤에 다시 볼 수 있습니다</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Shop</t>
+          <t>Available again in {0}s</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>미션</t>
+          <t>다이아</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Missions</t>
+          <t>Gems</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>자동강화</t>
+          <t>모든 단계를 끝냈습니다</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Auto</t>
+          <t>All tiers completed</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>공격</t>
+          <t>아직 달성하지 못했습니다</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ATK</t>
+          <t>Not achieved yet</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>보스 도전</t>
+          <t>오늘은 다 받았습니다 (내일 다시)</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Fight Boss</t>
+          <t>All claimed today (come back tomorrow)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>도전</t>
+          <t>다음 챕터에서 새 도전이 열립니다</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>A new challenge opens next chapter</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>공격력</t>
+          <t>도전 {0} — 모두 처치!</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>Attack</t>
+          <t>Challenge {0} — defeat them all!</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>공격속도</t>
+          <t>오늘 티켓을 다 썼습니다</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Attack Speed</t>
+          <t>No tickets left today</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>돈 획득량</t>
+          <t>다이아 광산</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Gold Gain</t>
+          <t>Gem Mine</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>총알 {0}</t>
+          <t>보스 던전 Lv.{0}</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Ammo {0}</t>
+          <t>Boss Dungeon Lv.{0}</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>비어 있음</t>
+          <t>도전 {0} 성공!</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Empty</t>
+          <t>Challenge {0} cleared!</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>무기</t>
+          <t>시간 초과</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Weapons</t>
+          <t>Time's up</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>스킨</t>
+          <t>채굴 끝!</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Skins</t>
+          <t>Mining done!</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>보급품</t>
+          <t>보스 처치!</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Supplies</t>
+          <t>Boss defeated!</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>UI/HUD.cs</t>
+          <t>Game/GameManager.cs</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>보스</t>
+          <t>절전모드</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Eco</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -1389,12 +1389,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>광산</t>
+          <t>상점</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Mine</t>
+          <t>Shop</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -1406,12 +1406,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>포기</t>
+          <t>미션</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Give Up</t>
+          <t>Missions</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>던전을 포기할까요?\n(사용한 티켓은 돌아오지 않습니다)</t>
+          <t>자동강화</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Give up the dungeon?\n(Used tickets are not refunded)</t>
+          <t>Auto</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1440,12 +1440,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>눌러서 강화!</t>
+          <t>공격</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Tap to upgrade!</t>
+          <t>ATK</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1457,12 +1457,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>절전 모드\n\n화면을 누르면 돌아옵니다</t>
+          <t>보스 도전</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Eco Mode\n\nTap the screen to return</t>
+          <t>Fight Boss</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -1474,12 +1474,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>남은 좀비 {0}</t>
+          <t>도전</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Zombies left {0}</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -1491,12 +1491,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>도전 {0}</t>
+          <t>공격력</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Challenge {0}</t>
+          <t>Attack</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1508,12 +1508,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>보스! {0}초</t>
+          <t>공격속도</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>BOSS! {0}s</t>
+          <t>Attack Speed</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>반복 사냥 중 — 강화 후 보스 도전!</t>
+          <t>돈 획득량</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Farming — upgrade, then fight the boss!</t>
+          <t>Gold Gain</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1542,267 +1542,267 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>그림 준비 중</t>
+          <t>총알 {0}</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Art coming soon</t>
+          <t>Ammo {0}</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>다이아 {0} 으로 살까요?</t>
+          <t>비어 있음</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Buy for {0} gems?</t>
+          <t>Empty</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>보유 효과</t>
+          <t>무기</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Owned bonus</t>
+          <t>Weapons</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 +{2}%</t>
+          <t>스킨</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Gold +{2}%</t>
+          <t>Skins</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>스킨 구매</t>
+          <t>보급품</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Buy Skin</t>
+          <t>Supplies</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>보유 효과 합계</t>
+          <t>보스</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Total owned bonus</t>
+          <t>Boss</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 획득량 +{2}%</t>
+          <t>광산</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Gold +{2}%</t>
+          <t>Mine</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>입는 중</t>
+          <t>포기</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Wearing</t>
+          <t>Give Up</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>보유</t>
+          <t>던전을 포기할까요?\n(사용한 티켓은 돌아오지 않습니다)</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Owned</t>
+          <t>Give up the dungeon?\n(Used tickets are not refunded)</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>눌러서 강화!</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Ad</t>
+          <t>Tap to upgrade!</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>{0} 으로 살까요?</t>
+          <t>절전 모드\n\n화면을 누르면 돌아옵니다</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Buy for {0}?</t>
+          <t>Eco Mode\n\nTap the screen to return</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>구매</t>
+          <t>남은 좀비 {0}</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>Zombies left {0}</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>{0}원</t>
+          <t>도전 {0}</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>KRW {0}</t>
+          <t>Challenge {0}</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>일반</t>
+          <t>보스! {0}초</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Common</t>
+          <t>BOSS! {0}s</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>고급</t>
+          <t>반복 사냥 중 — 강화 후 보스 도전!</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Uncommon</t>
+          <t>Farming — upgrade, then fight the boss!</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>UI/MenuPopups.cs</t>
+          <t>UI/HUD.cs</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>희귀</t>
+          <t>그림 준비 중</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Rare</t>
+          <t>Art coming soon</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -1814,12 +1814,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>영웅</t>
+          <t>다이아 {0} 으로 살까요?</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Epic</t>
+          <t>Buy for {0} gems?</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>전설</t>
+          <t>보유 효과</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Legendary</t>
+          <t>Owned bonus</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -1848,12 +1848,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>신화</t>
+          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 +{2}%</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>Mythic</t>
+          <t>ATK +{0}% · SPD +{1}% · Gold +{2}%</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -1865,12 +1865,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>초월</t>
+          <t>스킨 구매</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Transcendent</t>
+          <t>Buy Skin</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>불멸</t>
+          <t>보유 효과 합계</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Immortal</t>
+          <t>Total owned bonus</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>보급품 구매</t>
+          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 획득량 +{2}%</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Buy Supply</t>
+          <t>ATK +{0}% · SPD +{1}% · Gold +{2}%</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>공격 +{0}% · 속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
+          <t>입는 중</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
+          <t>Wearing</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -1933,12 +1933,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>보유 효과 합계 ({0}/{1})</t>
+          <t>보유</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Total owned bonus ({0}/{1})</t>
+          <t>Owned</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
+          <t>광고</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
+          <t>Ad</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -1967,12 +1967,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>챕터 {0}</t>
+          <t>{0} 으로 살까요?</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Ch. {0}</t>
+          <t>Buy for {0}?</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -1984,12 +1984,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>모든 단계 완료</t>
+          <t>보유 중</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>All tiers complete</t>
+          <t>Owned</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2001,12 +2001,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>완료</t>
+          <t>{0}원</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>KRW {0}</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>받기</t>
+          <t>일반</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Common</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -2035,12 +2035,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>설정</t>
+          <t>고급</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Settings</t>
+          <t>Uncommon</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>배경음</t>
+          <t>희귀</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>Rare</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>효과음</t>
+          <t>영웅</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Sound</t>
+          <t>Epic</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -2086,12 +2086,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>진동</t>
+          <t>전설</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Vibration</t>
+          <t>Legendary</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>던전에서는 바꿀 수 없습니다</t>
+          <t>신화</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Can't change during a dungeon</t>
+          <t>Mythic</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>저장</t>
+          <t>초월</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Save</t>
+          <t>Transcendent</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>저장했습니다 (기기 안)</t>
+          <t>불멸</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>Saved (on this device)</t>
+          <t>Immortal</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>불러오기 · 구매 복원 · 문의</t>
+          <t>보급품 구매</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Load · Restore · Contact</t>
+          <t>Buy Supply</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>클라우드 저장·결제 복원·문의는 준비 중입니다</t>
+          <t>공격 +{0}% · 속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Cloud save, restore and contact are coming soon</t>
+          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>켜짐</t>
+          <t>보유 효과 합계 ({0}/{1})</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>On</t>
+          <t>Total owned bonus ({0}/{1})</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2205,12 +2205,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>꺼짐</t>
+          <t>공격력 +{0}% · 공격속도 +{1}% · 돈 +{2}% · 보스 +{3}%</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Off</t>
+          <t>ATK +{0}% · SPD +{1}% · Gold +{2}% · Boss +{3}%</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2222,505 +2222,505 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>확인</t>
+          <t>챕터 {0}</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>Ch. {0}</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>시작</t>
+          <t>모든 단계 완료</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>All tiers complete</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>{0}초 안에 좀비 {1}마리를 모두 처치!</t>
+          <t>완료</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>Defeat all {1} zombies within {0}s!</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>화면을 눌러 분대를 직접 움직이면 빨라요</t>
+          <t>받기</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Tap the screen to move your squad — it's faster</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>보상: 다이아 {0} (챕터당 1번)</t>
+          <t>설정</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Reward: {0} gems (once per chapter)</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>보상 없음</t>
+          <t>배경음</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>No reward</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>다이아 광산 {0}단계</t>
+          <t>효과음</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Gem Mine Tier {0}</t>
+          <t>Sound</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>모든 공격이 1 피해로 고정!</t>
+          <t>진동</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>Every hit deals exactly 1 damage!</t>
+          <t>Vibration</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>오늘 티켓</t>
+          <t>던전에서는 바꿀 수 없습니다</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>Today's tickets</t>
+          <t>Can't change during a dungeon</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>{0}초 안에 {1}를 처치!</t>
+          <t>저장</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Defeat {1} within {0}s!</t>
+          <t>Save</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>체력</t>
+          <t>저장했습니다 (기기 안)</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>Saved (on this device)</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>보상: 다이아 {0}</t>
+          <t>불러오기 · 구매 복원 · 문의</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>Reward: {0} gems</t>
+          <t>Load · Restore · Contact</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>광고 보고</t>
+          <t>클라우드 저장·결제 복원·문의는 준비 중입니다</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Watch ad</t>
+          <t>Cloud save, restore and contact are coming soon</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>돌아가기</t>
+          <t>켜짐</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>On</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>UI/Popup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>총알</t>
+          <t>꺼짐</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Ammo</t>
+          <t>Off</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/MenuPopups.cs</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>리더</t>
+          <t>확인</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Leader</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>동료 1</t>
+          <t>시작</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Ally 1</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>동료 2</t>
+          <t>{0}초 안에 좀비 {1}마리를 모두 처치!</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Ally 2</t>
+          <t>Defeat all {1} zombies within {0}s!</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>장착</t>
+          <t>화면을 눌러 분대를 직접 움직이면 빨라요</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Equip</t>
+          <t>Tap the screen to move your squad — it's faster</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>강화</t>
+          <t>보상: 다이아 {0} (챕터당 1번)</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Enhance</t>
+          <t>Reward: {0} gems (once per chapter)</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>D 등급 총알 획득!</t>
+          <t>보상 없음</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Got D grade ammo!</t>
+          <t>No reward</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>같은 등급 두 개를 끌어다 겹치면 합성!\n장착 칸을 누르면 슬롯 강화 · 남는 총알은 분해 → 다이아</t>
+          <t>다이아 광산 {0}단계</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Drag two of the same grade together to merge!\nTap an equip slot to enhance · Salvage spares → gems</t>
+          <t>Gem Mine Tier {0}</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>뽑기</t>
+          <t>모든 공격이 1 피해로 고정!</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Draw</t>
+          <t>Every hit deals exactly 1 damage!</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>총알을 누르면 정보가 나옵니다.\n장착 칸으로 끌어다 놓으면 장착!</t>
+          <t>오늘 티켓</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Tap ammo to see its info.\nDrag it onto an equip slot to equip!</t>
+          <t>Today's tickets</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>{0}발</t>
+          <t>{0}초 안에 {1}를 처치!</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>{0} pellets</t>
+          <t>Defeat {1} within {0}s!</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>{0}마리 관통</t>
+          <t>체력</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>pierces {0}</t>
+          <t>HP</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>범위 {0}</t>
+          <t>보상: 다이아 {0}</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>radius {0}</t>
+          <t>Reward: {0} gems</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>일직선 전부</t>
+          <t>광고 보고</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>hits the whole line</t>
+          <t>Watch ad</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>공격력 {0} · 연사 {1}초</t>
+          <t>돌아가기</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>ATK {0} · fires every {1}s</t>
+          <t>Back</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>UI/WeaponPopup.cs</t>
+          <t>UI/Popup.cs</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>넘친 공속 → 공격 x{0}</t>
+          <t>총알</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Excess speed → ATK x{0}</t>
+          <t>Ammo</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>(칸 +{0}, 이 등급은 +{1}까지)</t>
+          <t>리더</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>(slot +{0}, this grade caps at +{1})</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>최대 +{0}</t>
+          <t>동료 1</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>max +{0}</t>
+          <t>Ally 1</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -2766,12 +2766,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>슬롯 강화 +{0}</t>
+          <t>동료 2</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Slot +{0}</t>
+          <t>Ally 2</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>공격 +{0}% · 속도 +{1}% · 보스 +{2}%</t>
+          <t>장착</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>ATK +{0}% · SPD +{1}% · Boss +{2}%</t>
+          <t>Equip</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -2800,12 +2800,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>분해</t>
+          <t>강화</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Salvage</t>
+          <t>Enhance</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>해제</t>
+          <t>D 등급 총알 획득!</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Unequip</t>
+          <t>Got D grade ammo!</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -2834,12 +2834,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>{0} 을(를) 분해할까요?</t>
+          <t>같은 등급 두 개를 끌어다 겹치면 합성!\n장착 칸을 누르면 슬롯 강화 · 남는 총알은 분해 → 다이아</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Salvage {0}?</t>
+          <t>Drag two of the same grade together to merge!\nTap an equip slot to enhance · Salvage spares → gems</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -2851,12 +2851,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>슬롯 강화</t>
+          <t>뽑기</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Slot Enhance</t>
+          <t>Draw</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>성공 확률 {0}%</t>
+          <t>총알을 누르면 정보가 나옵니다.\n장착 칸으로 끌어다 놓으면 장착!</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Success rate {0}%</t>
+          <t>Tap ammo to see its info.\nDrag it onto an equip slot to equip!</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -2885,12 +2885,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>공격속도 +{0}% · 보스 피해 +{1}%</t>
+          <t>{0}발</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>SPD +{0}% · Boss DMG +{1}%</t>
+          <t>{0} pellets</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -2902,12 +2902,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>강화 성공!</t>
+          <t>{0}마리 관통</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Enhanced!</t>
+          <t>pierces {0}</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>강화 실패… (재료만 사라짐)</t>
+          <t>범위 {0}</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Enhance failed… (materials lost)</t>
+          <t>radius {0}</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>합성!</t>
+          <t>일직선 전부</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Merged!</t>
+          <t>hits the whole line</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>장착 중인 총알은 해제한 뒤 합성할 수 있습니다</t>
+          <t>공격력 {0} · 연사 {1}초</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Unequip ammo before merging it</t>
+          <t>ATK {0} · fires every {1}s</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -2970,267 +2970,267 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>기본 카피</t>
+          <t>넘친 공속 → 공격 x{0}</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Classic Capy</t>
+          <t>Excess speed → ATK x{0}</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>밀짚모자</t>
+          <t>(칸 +{0}, 이 등급은 +{1}까지)</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Straw Hat</t>
+          <t>(slot +{0}, this grade caps at +{1})</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>천사 날개</t>
+          <t>최대 +{0}</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Angel Wings</t>
+          <t>max +{0}</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>새싹</t>
+          <t>슬롯 강화 +{0}</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Sprout</t>
+          <t>Slot +{0}</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>꿀꿀 돼지</t>
+          <t>공격 +{0}% · 속도 +{1}% · 보스 +{2}%</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Piggy</t>
+          <t>ATK +{0}% · SPD +{1}% · Boss +{2}%</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>악어 잠옷</t>
+          <t>분해</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Croc Pajamas</t>
+          <t>Salvage</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>원시인</t>
+          <t>해제</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Caveman</t>
+          <t>Unequip</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>검은 두건</t>
+          <t>{0} 을(를) 분해할까요?</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Black Hood</t>
+          <t>Salvage {0}?</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>그림자 망토</t>
+          <t>슬롯 강화</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Shadow Cloak</t>
+          <t>Slot Enhance</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>공룡 잠옷</t>
+          <t>성공 확률 {0}%</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Dino Pajamas</t>
+          <t>Success rate {0}%</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>모험가 배낭</t>
+          <t>공격속도 +{0}% · 보스 피해 +{1}%</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Explorer's Pack</t>
+          <t>SPD +{0}% · Boss DMG +{1}%</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>박쥐 날개</t>
+          <t>강화 성공!</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Bat Wings</t>
+          <t>Enhanced!</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>멜빵바지</t>
+          <t>강화 실패… (재료만 사라짐)</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Overalls</t>
+          <t>Enhance failed… (materials lost)</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>꼬꼬 잠옷</t>
+          <t>합성!</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Chicken Pajamas</t>
+          <t>Merged!</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>빨간 망토</t>
+          <t>장착 중인 총알은 해제한 뒤 합성할 수 있습니다</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>Red Cape</t>
+          <t>Unequip ammo before merging it</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>Skin_Table.Name</t>
+          <t>UI/WeaponPopup.cs</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>상어 잠옷</t>
+          <t>기본 카피</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Shark Pajamas</t>
+          <t>Classic Capy</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -3242,12 +3242,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>줄무늬 고양이</t>
+          <t>밀짚모자</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Tabby Cat</t>
+          <t>Straw Hat</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>해적 선장</t>
+          <t>천사 날개</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Pirate Captain</t>
+          <t>Angel Wings</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -3276,267 +3276,267 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>기본탄_D</t>
+          <t>새싹</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_D</t>
+          <t>Sprout</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>산탄_D</t>
+          <t>꿀꿀 돼지</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_D</t>
+          <t>Piggy</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>속사탄_D</t>
+          <t>악어 잠옷</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_D</t>
+          <t>Croc Pajamas</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>기본탄_C</t>
+          <t>원시인</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_C</t>
+          <t>Caveman</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>산탄_C</t>
+          <t>검은 두건</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_C</t>
+          <t>Black Hood</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>관통탄_C</t>
+          <t>그림자 망토</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_C</t>
+          <t>Shadow Cloak</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>기본탄_B</t>
+          <t>공룡 잠옷</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_B</t>
+          <t>Dino Pajamas</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>산탄_B</t>
+          <t>모험가 배낭</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_B</t>
+          <t>Explorer's Pack</t>
         </is>
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>속사탄_B</t>
+          <t>박쥐 날개</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_B</t>
+          <t>Bat Wings</t>
         </is>
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>관통탄_B</t>
+          <t>멜빵바지</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_B</t>
+          <t>Overalls</t>
         </is>
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>기본탄_A</t>
+          <t>꼬꼬 잠옷</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_A</t>
+          <t>Chicken Pajamas</t>
         </is>
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>산탄_A</t>
+          <t>빨간 망토</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_A</t>
+          <t>Red Cape</t>
         </is>
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>속사탄_A</t>
+          <t>상어 잠옷</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_A</t>
+          <t>Shark Pajamas</t>
         </is>
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>관통탄_A</t>
+          <t>줄무늬 고양이</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_A</t>
+          <t>Tabby Cat</t>
         </is>
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>기본탄_S</t>
+          <t>해적 선장</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_S</t>
+          <t>Pirate Captain</t>
         </is>
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Weapon_Master.Name</t>
+          <t>Skin_Table.Name</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>산탄_S</t>
+          <t>기본탄_D</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_S</t>
+          <t>Basic Round_D</t>
         </is>
       </c>
       <c r="C183" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>속사탄_S</t>
+          <t>산탄_D</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_S</t>
+          <t>Buckshot_D</t>
         </is>
       </c>
       <c r="C184" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>관통탄_S</t>
+          <t>속사탄_D</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_S</t>
+          <t>Rapid Round_D</t>
         </is>
       </c>
       <c r="C185" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_S</t>
+          <t>기본탄_C</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_S</t>
+          <t>Basic Round_C</t>
         </is>
       </c>
       <c r="C186" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_S</t>
+          <t>산탄_C</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>Missile_S</t>
+          <t>Buckshot_C</t>
         </is>
       </c>
       <c r="C187" s="2" t="inlineStr">
@@ -3616,12 +3616,12 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SS</t>
+          <t>관통탄_C</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SS</t>
+          <t>Piercing Round_C</t>
         </is>
       </c>
       <c r="C188" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>산탄_SS</t>
+          <t>기본탄_B</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SS</t>
+          <t>Basic Round_B</t>
         </is>
       </c>
       <c r="C189" s="2" t="inlineStr">
@@ -3650,12 +3650,12 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SS</t>
+          <t>산탄_B</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SS</t>
+          <t>Buckshot_B</t>
         </is>
       </c>
       <c r="C190" s="2" t="inlineStr">
@@ -3667,12 +3667,12 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SS</t>
+          <t>속사탄_B</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SS</t>
+          <t>Rapid Round_B</t>
         </is>
       </c>
       <c r="C191" s="2" t="inlineStr">
@@ -3684,12 +3684,12 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SS</t>
+          <t>관통탄_B</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SS</t>
+          <t>Piercing Round_B</t>
         </is>
       </c>
       <c r="C192" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SS</t>
+          <t>기본탄_A</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>Missile_SS</t>
+          <t>Basic Round_A</t>
         </is>
       </c>
       <c r="C193" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SSS</t>
+          <t>산탄_A</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SSS</t>
+          <t>Buckshot_A</t>
         </is>
       </c>
       <c r="C194" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>산탄_SSS</t>
+          <t>속사탄_A</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SSS</t>
+          <t>Rapid Round_A</t>
         </is>
       </c>
       <c r="C195" s="2" t="inlineStr">
@@ -3752,12 +3752,12 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SSS</t>
+          <t>관통탄_A</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SSS</t>
+          <t>Piercing Round_A</t>
         </is>
       </c>
       <c r="C196" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SSS</t>
+          <t>기본탄_S</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SSS</t>
+          <t>Basic Round_S</t>
         </is>
       </c>
       <c r="C197" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SSS</t>
+          <t>산탄_S</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SSS</t>
+          <t>Buckshot_S</t>
         </is>
       </c>
       <c r="C198" s="2" t="inlineStr">
@@ -3803,12 +3803,12 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SSS</t>
+          <t>속사탄_S</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>Missile_SSS</t>
+          <t>Rapid Round_S</t>
         </is>
       </c>
       <c r="C199" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>기본탄_R</t>
+          <t>관통탄_S</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_R</t>
+          <t>Piercing Round_S</t>
         </is>
       </c>
       <c r="C200" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>산탄_R</t>
+          <t>레이저탄_S</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_R</t>
+          <t>Laser Round_S</t>
         </is>
       </c>
       <c r="C201" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>속사탄_R</t>
+          <t>미사일탄_S</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_R</t>
+          <t>Missile_S</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>관통탄_R</t>
+          <t>기본탄_SS</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_R</t>
+          <t>Basic Round_SS</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
@@ -3888,12 +3888,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_R</t>
+          <t>산탄_SS</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_R</t>
+          <t>Buckshot_SS</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_R</t>
+          <t>속사탄_SS</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>Missile_R</t>
+          <t>Rapid Round_SS</t>
         </is>
       </c>
       <c r="C205" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SR</t>
+          <t>관통탄_SS</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SR</t>
+          <t>Piercing Round_SS</t>
         </is>
       </c>
       <c r="C206" s="2" t="inlineStr">
@@ -3939,12 +3939,12 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>산탄_SR</t>
+          <t>레이저탄_SS</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SR</t>
+          <t>Laser Round_SS</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SR</t>
+          <t>미사일탄_SS</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SR</t>
+          <t>Missile_SS</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SR</t>
+          <t>기본탄_SSS</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SR</t>
+          <t>Basic Round_SSS</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SR</t>
+          <t>산탄_SSS</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SR</t>
+          <t>Buckshot_SSS</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SR</t>
+          <t>속사탄_SSS</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Missile_SR</t>
+          <t>Rapid Round_SSS</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SSR</t>
+          <t>관통탄_SSS</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SSR</t>
+          <t>Piercing Round_SSS</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
@@ -4041,12 +4041,12 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>산탄_SSR</t>
+          <t>레이저탄_SSS</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SSR</t>
+          <t>Laser Round_SSS</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SSR</t>
+          <t>미사일탄_SSS</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SSR</t>
+          <t>Missile_SSS</t>
         </is>
       </c>
       <c r="C214" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SSR</t>
+          <t>기본탄_R</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SSR</t>
+          <t>Basic Round_R</t>
         </is>
       </c>
       <c r="C215" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SSR</t>
+          <t>산탄_R</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SSR</t>
+          <t>Buckshot_R</t>
         </is>
       </c>
       <c r="C216" s="2" t="inlineStr">
@@ -4109,12 +4109,12 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SSR</t>
+          <t>속사탄_R</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Missile_SSR</t>
+          <t>Rapid Round_R</t>
         </is>
       </c>
       <c r="C217" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>기본탄_U</t>
+          <t>관통탄_R</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_U</t>
+          <t>Piercing Round_R</t>
         </is>
       </c>
       <c r="C218" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>산탄_U</t>
+          <t>레이저탄_R</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_U</t>
+          <t>Laser Round_R</t>
         </is>
       </c>
       <c r="C219" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>속사탄_U</t>
+          <t>미사일탄_R</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_U</t>
+          <t>Missile_R</t>
         </is>
       </c>
       <c r="C220" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>관통탄_U</t>
+          <t>기본탄_SR</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_U</t>
+          <t>Basic Round_SR</t>
         </is>
       </c>
       <c r="C221" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_U</t>
+          <t>산탄_SR</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_U</t>
+          <t>Buckshot_SR</t>
         </is>
       </c>
       <c r="C222" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_U</t>
+          <t>속사탄_SR</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Missile_U</t>
+          <t>Rapid Round_SR</t>
         </is>
       </c>
       <c r="C223" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SU</t>
+          <t>관통탄_SR</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SU</t>
+          <t>Piercing Round_SR</t>
         </is>
       </c>
       <c r="C224" s="2" t="inlineStr">
@@ -4245,12 +4245,12 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>산탄_SU</t>
+          <t>레이저탄_SR</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SU</t>
+          <t>Laser Round_SR</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
@@ -4262,12 +4262,12 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SU</t>
+          <t>미사일탄_SR</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SU</t>
+          <t>Missile_SR</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
@@ -4279,12 +4279,12 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SU</t>
+          <t>기본탄_SSR</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SU</t>
+          <t>Basic Round_SSR</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SU</t>
+          <t>산탄_SSR</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SU</t>
+          <t>Buckshot_SSR</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
@@ -4313,12 +4313,12 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SU</t>
+          <t>속사탄_SSR</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Missile_SU</t>
+          <t>Rapid Round_SSR</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>기본탄_SSU</t>
+          <t>관통탄_SSR</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Basic Round_SSU</t>
+          <t>Piercing Round_SSR</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
@@ -4347,12 +4347,12 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>산탄_SSU</t>
+          <t>레이저탄_SSR</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Buckshot_SSU</t>
+          <t>Laser Round_SSR</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
@@ -4364,12 +4364,12 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>속사탄_SSU</t>
+          <t>미사일탄_SSR</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Rapid Round_SSU</t>
+          <t>Missile_SSR</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>관통탄_SSU</t>
+          <t>기본탄_U</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Piercing Round_SSU</t>
+          <t>Basic Round_U</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_SSU</t>
+          <t>산탄_U</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Laser Round_SSU</t>
+          <t>Buckshot_U</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
@@ -4415,12 +4415,12 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>미사일탄_SSU</t>
+          <t>속사탄_U</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>Missile_SSU</t>
+          <t>Rapid Round_U</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
@@ -4432,471 +4432,471 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>기어오는 좀비</t>
+          <t>관통탄_U</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Crawler</t>
+          <t>Piercing Round_U</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>칼 좀비</t>
+          <t>레이저탄_U</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Knife Zombie</t>
+          <t>Laser Round_U</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>좀비</t>
+          <t>미사일탄_U</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>Zombie</t>
+          <t>Missile_U</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>모자 좀비</t>
+          <t>기본탄_SU</t>
         </is>
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>Hat Zombie</t>
+          <t>Basic Round_SU</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>양동이 좀비</t>
+          <t>산탄_SU</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
         <is>
-          <t>Bucket Zombie</t>
+          <t>Buckshot_SU</t>
         </is>
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>갑옷 좀비</t>
+          <t>속사탄_SU</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>Armored Zombie</t>
+          <t>Rapid Round_SU</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>방망이 좀비</t>
+          <t>관통탄_SU</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>Bat Zombie</t>
+          <t>Piercing Round_SU</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>농부 좀비</t>
+          <t>레이저탄_SU</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
         <is>
-          <t>Farmer Zombie</t>
+          <t>Laser Round_SU</t>
         </is>
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>미라</t>
+          <t>미사일탄_SU</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>Mummy</t>
+          <t>Missile_SU</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>뚱보 좀비</t>
+          <t>기본탄_SSU</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>Fat Zombie</t>
+          <t>Basic Round_SSU</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>사신 좀비</t>
+          <t>산탄_SSU</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>Reaper Zombie</t>
+          <t>Buckshot_SSU</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>변이 오우거</t>
+          <t>속사탄_SSU</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>Mutant Ogre</t>
+          <t>Rapid Round_SSU</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Zombie_Master.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>비상 건빵</t>
+          <t>관통탄_SSU</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>Emergency Crackers</t>
+          <t>Piercing Round_SSU</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
         <is>
-          <t>통조림 캔</t>
+          <t>레이저탄_SSU</t>
         </is>
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>Canned Food</t>
+          <t>Laser Round_SSU</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="2" t="inlineStr">
         <is>
-          <t>정수 필터</t>
+          <t>미사일탄_SSU</t>
         </is>
       </c>
       <c r="B250" s="2" t="inlineStr">
         <is>
-          <t>Water Filter</t>
+          <t>Missile_SSU</t>
         </is>
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Weapon_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
         <is>
-          <t>야전 반합</t>
+          <t>기어오는 좀비</t>
         </is>
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>Mess Kit</t>
+          <t>Crawler</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="inlineStr">
         <is>
-          <t>에너지 바</t>
+          <t>칼 좀비</t>
         </is>
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>Energy Bar</t>
+          <t>Knife Zombie</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="2" t="inlineStr">
         <is>
-          <t>구급 상자</t>
+          <t>좀비</t>
         </is>
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>First Aid Kit</t>
+          <t>Zombie</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
         <is>
-          <t>아드레날린 주사</t>
+          <t>모자 좀비</t>
         </is>
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>Adrenaline Shot</t>
+          <t>Hat Zombie</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="2" t="inlineStr">
         <is>
-          <t>군용 무전기</t>
+          <t>양동이 좀비</t>
         </is>
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>Field Radio</t>
+          <t>Bucket Zombie</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
         <is>
-          <t>야간 투시경</t>
+          <t>갑옷 좀비</t>
         </is>
       </c>
       <c r="B256" s="2" t="inlineStr">
         <is>
-          <t>Night Vision</t>
+          <t>Armored Zombie</t>
         </is>
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
         <is>
-          <t>방탄 조끼</t>
+          <t>방망이 좀비</t>
         </is>
       </c>
       <c r="B257" s="2" t="inlineStr">
         <is>
-          <t>Bulletproof Vest</t>
+          <t>Bat Zombie</t>
         </is>
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="inlineStr">
         <is>
-          <t>전술 탄띠</t>
+          <t>농부 좀비</t>
         </is>
       </c>
       <c r="B258" s="2" t="inlineStr">
         <is>
-          <t>Tactical Bandolier</t>
+          <t>Farmer Zombie</t>
         </is>
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="inlineStr">
         <is>
-          <t>고농축 스팀팩</t>
+          <t>미라</t>
         </is>
       </c>
       <c r="B259" s="2" t="inlineStr">
         <is>
-          <t>Mega Stimpack</t>
+          <t>Mummy</t>
         </is>
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="inlineStr">
         <is>
-          <t>열화우라늄 탄심</t>
+          <t>뚱보 좀비</t>
         </is>
       </c>
       <c r="B260" s="2" t="inlineStr">
         <is>
-          <t>DU Core</t>
+          <t>Fat Zombie</t>
         </is>
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="inlineStr">
         <is>
-          <t>냉각 모듈</t>
+          <t>사신 좀비</t>
         </is>
       </c>
       <c r="B261" s="2" t="inlineStr">
         <is>
-          <t>Cooling Module</t>
+          <t>Reaper Zombie</t>
         </is>
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>플라즈마 배터리</t>
+          <t>변이 오우거</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
         <is>
-          <t>Plasma Battery</t>
+          <t>Mutant Ogre</t>
         </is>
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Name</t>
+          <t>Zombie_Master.Name</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="inlineStr">
         <is>
-          <t>양자 증폭기</t>
+          <t>비상 건빵</t>
         </is>
       </c>
       <c r="B263" s="2" t="inlineStr">
         <is>
-          <t>Quantum Amplifier</t>
+          <t>Emergency Crackers</t>
         </is>
       </c>
       <c r="C263" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
     <row r="264">
       <c r="A264" s="2" t="inlineStr">
         <is>
-          <t>중력 제어 코어</t>
+          <t>통조림 캔</t>
         </is>
       </c>
       <c r="B264" s="2" t="inlineStr">
         <is>
-          <t>Gravity Core</t>
+          <t>Canned Food</t>
         </is>
       </c>
       <c r="C264" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
     <row r="265">
       <c r="A265" s="2" t="inlineStr">
         <is>
-          <t>나노 수복 혈청</t>
+          <t>정수 필터</t>
         </is>
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>Nano Serum</t>
+          <t>Water Filter</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
@@ -4942,12 +4942,12 @@
     <row r="266">
       <c r="A266" s="2" t="inlineStr">
         <is>
-          <t>바이오 리액터</t>
+          <t>야전 반합</t>
         </is>
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>Bio Reactor</t>
+          <t>Mess Kit</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
@@ -4959,12 +4959,12 @@
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
         <is>
-          <t>초전도 코일</t>
+          <t>에너지 바</t>
         </is>
       </c>
       <c r="B267" s="2" t="inlineStr">
         <is>
-          <t>Superconductor Coil</t>
+          <t>Energy Bar</t>
         </is>
       </c>
       <c r="C267" s="2" t="inlineStr">
@@ -4976,12 +4976,12 @@
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>암흑물질 셀</t>
+          <t>구급 상자</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>Dark Matter Cell</t>
+          <t>First Aid Kit</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>차원 도약 엔진</t>
+          <t>아드레날린 주사</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>Warp Engine</t>
+          <t>Adrenaline Shot</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
@@ -5010,12 +5010,12 @@
     <row r="270">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>항성 에너지 핵</t>
+          <t>군용 무전기</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>Stellar Core</t>
+          <t>Field Radio</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
@@ -5027,12 +5027,12 @@
     <row r="271">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>영구기관 모듈</t>
+          <t>야간 투시경</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>Perpetual Engine</t>
+          <t>Night Vision</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
@@ -5044,12 +5044,12 @@
     <row r="272">
       <c r="A272" s="2" t="inlineStr">
         <is>
-          <t>카피바라의 성배</t>
+          <t>방탄 조끼</t>
         </is>
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>Capybara Grail</t>
+          <t>Bulletproof Vest</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
@@ -5061,1151 +5061,1151 @@
     <row r="273">
       <c r="A273" s="2" t="inlineStr">
         <is>
-          <t>태초</t>
+          <t>전술 탄띠</t>
         </is>
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>Primordial</t>
+          <t>Tactical Bandolier</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>Supply_Collection.Grade</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="inlineStr">
         <is>
-          <t>좀비 처치하기</t>
+          <t>고농축 스팀팩</t>
         </is>
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>Defeat zombies</t>
+          <t>Mega Stimpack</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="inlineStr">
         <is>
-          <t>스테이지 클리어하기</t>
+          <t>열화우라늄 탄심</t>
         </is>
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>Clear stages</t>
+          <t>DU Core</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="inlineStr">
         <is>
-          <t>광산 플레이하기</t>
+          <t>냉각 모듈</t>
         </is>
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>Play the mine</t>
+          <t>Cooling Module</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="inlineStr">
         <is>
-          <t>보스 처치하기</t>
+          <t>플라즈마 배터리</t>
         </is>
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>Defeat bosses</t>
+          <t>Plasma Battery</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
         <is>
-          <t>총알 합성하기</t>
+          <t>양자 증폭기</t>
         </is>
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>Merge ammo</t>
+          <t>Quantum Amplifier</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Mission_Master.Mission_Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
         <is>
-          <t>공격력 x2 (5분)</t>
+          <t>중력 제어 코어</t>
         </is>
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>Attack x2 (5 min)</t>
+          <t>Gravity Core</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="inlineStr">
         <is>
-          <t>광고 1편 · 연속 시청 시 시간 누적</t>
+          <t>나노 수복 혈청</t>
         </is>
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>1 ad · time stacks when watched again</t>
+          <t>Nano Serum</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="inlineStr">
         <is>
-          <t>돈 획득량 x2 (5분)</t>
+          <t>바이오 리액터</t>
         </is>
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>Gold x2 (5 min)</t>
+          <t>Bio Reactor</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="inlineStr">
         <is>
-          <t>모든 광고 제거</t>
+          <t>초전도 코일</t>
         </is>
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>Remove All Ads</t>
+          <t>Superconductor Coil</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="inlineStr">
         <is>
-          <t>보상형 광고도 바로 보상</t>
+          <t>암흑물질 셀</t>
         </is>
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>Rewards without watching ads</t>
+          <t>Dark Matter Cell</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="inlineStr">
         <is>
-          <t>자동강화 패키지</t>
+          <t>차원 도약 엔진</t>
         </is>
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>Auto Upgrade Pack</t>
+          <t>Warp Engine</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="2" t="inlineStr">
         <is>
-          <t>하단 강화 자동 + 다이아 500</t>
+          <t>항성 에너지 핵</t>
         </is>
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>Upgrades buy themselves + 500 gems</t>
+          <t>Stellar Core</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
         <is>
-          <t>다이아 한 줌 (500)</t>
+          <t>영구기관 모듈</t>
         </is>
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>Handful of Gems (500)</t>
+          <t>Perpetual Engine</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
         <is>
-          <t>다이아 500개 즉시 획득</t>
+          <t>카피바라의 성배</t>
         </is>
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>Get 500 gems now</t>
+          <t>Capybara Grail</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Supply_Collection.Name</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
         <is>
-          <t>다이아 주머니 (1,800)</t>
+          <t>태초</t>
         </is>
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>Pouch of Gems (1,800)</t>
+          <t>Primordial</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Supply_Collection.Grade</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="inlineStr">
         <is>
-          <t>다이아 1,800개 즉시 획득</t>
+          <t>좀비 처치하기</t>
         </is>
       </c>
       <c r="B289" s="2" t="inlineStr">
         <is>
-          <t>Get 1,800 gems now</t>
+          <t>Defeat zombies</t>
         </is>
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>다이아 상자 (4,200)</t>
+          <t>스테이지 클리어하기</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>Chest of Gems (4,200)</t>
+          <t>Clear stages</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>다이아 4,200개 즉시 획득</t>
+          <t>광산 플레이하기</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>Get 4,200 gems now</t>
+          <t>Play the mine</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>무료 다이아</t>
+          <t>보스 처치하기</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>Free Gems</t>
+          <t>Defeat bosses</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Name</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>광고 1편 · 다이아 40 · 하루 3번</t>
+          <t>총알 합성하기</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>1 ad · 40 gems · 3 times a day</t>
+          <t>Merge ammo</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Shop_Products.Description</t>
+          <t>Mission_Master.Mission_Name</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
         <is>
-          <t>폐허 숲길</t>
+          <t>공격력 x2 (5분)</t>
         </is>
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>Ruined Forest Trail</t>
+          <t>Attack x2 (5 min)</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
         <is>
-          <t>오염된 해안</t>
+          <t>광고 1편 · 연속 시청 시 시간 누적</t>
         </is>
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>Polluted Coast</t>
+          <t>1 ad · time stacks when watched again</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
         <is>
-          <t>사막 도로</t>
+          <t>돈 획득량 x2 (5분)</t>
         </is>
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>Desert Road</t>
+          <t>Gold x2 (5 min)</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
         <is>
-          <t>얼어붙은 설원</t>
+          <t>모든 광고 제거</t>
         </is>
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>Frozen Snowfield</t>
+          <t>Remove All Ads</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" s="2" t="inlineStr">
         <is>
-          <t>지하 연구소</t>
+          <t>보상형 광고도 바로 보상</t>
         </is>
       </c>
       <c r="B298" s="2" t="inlineStr">
         <is>
-          <t>Underground Lab</t>
+          <t>Rewards without watching ads</t>
         </is>
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>오염 구역</t>
+          <t>자동강화 패키지</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>Contaminated Zone</t>
+          <t>Auto Upgrade Pack</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Chapter_Summary.Biome_Name</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>무기는 다이아 100 또는 도전 클리어 에서 열립니다</t>
+          <t>하단 강화 자동 + 다이아 500</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>Weapons unlock with 100 gems or a challenge clear</t>
+          <t>Upgrades buy themselves + 500 gems</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>무기 메뉴가 열렸습니다!</t>
+          <t>다이아 한 줌 (500)</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>Weapons unlocked!</t>
+          <t>Handful of Gems (500)</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>Stage 1-2 에서 열립니다</t>
+          <t>다이아 500개 즉시 획득</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 1-2</t>
+          <t>Get 500 gems now</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
         <is>
-          <t>스킨이 열렸습니다!</t>
+          <t>다이아 주머니 (1,800)</t>
         </is>
       </c>
       <c r="B303" s="2" t="inlineStr">
         <is>
-          <t>Skins unlocked!</t>
+          <t>Pouch of Gems (1,800)</t>
         </is>
       </c>
       <c r="C303" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>Stage 4-1 에서 열립니다</t>
+          <t>다이아 1,800개 즉시 획득</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 4-1</t>
+          <t>Get 1,800 gems now</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>다이아 광산이 열렸습니다!</t>
+          <t>다이아 상자 (4,200)</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>Gem Mine unlocked!</t>
+          <t>Chest of Gems (4,200)</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>Stage 6-1 에서 열립니다</t>
+          <t>다이아 4,200개 즉시 획득</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 6-1</t>
+          <t>Get 4,200 gems now</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>보급품이 열렸습니다!</t>
+          <t>무료 다이아</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>Supplies unlocked!</t>
+          <t>Free Gems</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
         <is>
-          <t>Stage 10-1 에서 열립니다</t>
+          <t>광고 1편 · 다이아 40 · 하루 3번</t>
         </is>
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>Unlocks at Stage 10-1</t>
+          <t>1 ad · 40 gems · 3 times a day</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Lock_Toast_Message</t>
+          <t>Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
         <is>
-          <t>보스 던전이 열렸습니다!</t>
+          <t>폐허 숲길</t>
         </is>
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>Boss Dungeon unlocked!</t>
+          <t>Ruined Forest Trail</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
         <is>
-          <t>큰 푸른 보석</t>
+          <t>오염된 해안</t>
         </is>
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>Big Blue Gem</t>
+          <t>Polluted Coast</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="inlineStr">
         <is>
-          <t>작은 푸른 보석</t>
+          <t>사막 도로</t>
         </is>
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>Small Blue Gem</t>
+          <t>Desert Road</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
         <is>
-          <t>회색 바위</t>
+          <t>얼어붙은 설원</t>
         </is>
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>Gray Rock</t>
+          <t>Frozen Snowfield</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
         <is>
-          <t>거대 황금 크리스탈</t>
+          <t>지하 연구소</t>
         </is>
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>Huge Gold Crystal</t>
+          <t>Underground Lab</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Mine_Ore_Spec.Name_KR</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="inlineStr">
         <is>
-          <t>강제 광고 제거</t>
+          <t>오염 구역</t>
         </is>
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>Remove Forced Ads</t>
+          <t>Contaminated Zone</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Name</t>
+          <t>Chapter_Summary.Biome_Name</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="inlineStr">
         <is>
-          <t>자동 전면 광고 제거 + 돼지저금통</t>
+          <t>무기는 다이아 100 또는 도전 클리어 에서 열립니다</t>
         </is>
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>No more forced ads + piggy bank</t>
+          <t>Weapons unlock with 100 gems or a challenge clear</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
         <is>
-          <t>영구 3배 버프</t>
+          <t>무기 메뉴가 열렸습니다!</t>
         </is>
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>Permanent x3 Buff</t>
+          <t>Weapons unlocked!</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
         <is>
-          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
+          <t>Stage 1-2 에서 열립니다</t>
         </is>
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>Permanent x3 attack &amp; gold + 1,000 gems</t>
+          <t>Unlocks at Stage 1-2</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" s="2" t="inlineStr">
         <is>
-          <t>광산 티켓 확장</t>
+          <t>스킨이 열렸습니다!</t>
         </is>
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>Mine Ticket Pack</t>
+          <t>Skins unlocked!</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="2" t="inlineStr">
         <is>
-          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
+          <t>Stage 4-1 에서 열립니다</t>
         </is>
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>Daily mine tickets 2 → 6 + 500 gems</t>
+          <t>Unlocks at Stage 4-1</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="2" t="inlineStr">
         <is>
-          <t>핫딜 레이저 총알</t>
+          <t>다이아 광산이 열렸습니다!</t>
         </is>
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>Hot Deal: Laser Ammo</t>
+          <t>Gem Mine unlocked!</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
         <is>
-          <t>레이저탄_S 즉시 지급</t>
+          <t>Stage 6-1 에서 열립니다</t>
         </is>
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>Get a Laser Round_S now</t>
+          <t>Unlocks at Stage 6-1</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="2" t="inlineStr">
         <is>
-          <t>30분 방치 골드 상자</t>
+          <t>보급품이 열렸습니다!</t>
         </is>
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>30-min Gold Chest</t>
+          <t>Supplies unlocked!</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Name</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="2" t="inlineStr">
         <is>
-          <t>현재 스테이지 기준 600마리 처치 골드</t>
+          <t>Stage 10-1 에서 열립니다</t>
         </is>
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>Gold of 600 zombies at your current stage</t>
+          <t>Unlocks at Stage 10-1</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Lock_Toast_Message</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
         <is>
-          <t>S 등급 레이저 건 즉시 지급</t>
+          <t>보스 던전이 열렸습니다!</t>
         </is>
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>Get an S grade Laser Gun now</t>
+          <t>Boss Dungeon unlocked!</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Shop_Products.Description</t>
+          <t>Unlock_Roadmap.Unlock_Banner_Message</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="2" t="inlineStr">
         <is>
-          <t>리볼버</t>
+          <t>큰 푸른 보석</t>
         </is>
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>Revolver</t>
+          <t>Big Blue Gem</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
         <is>
-          <t>소드오프 샷건</t>
+          <t>작은 푸른 보석</t>
         </is>
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>Sawed-off Shotgun</t>
+          <t>Small Blue Gem</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="2" t="inlineStr">
         <is>
-          <t>우지</t>
+          <t>회색 바위</t>
         </is>
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>Uzi</t>
+          <t>Gray Rock</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="2" t="inlineStr">
         <is>
-          <t>상위 리볼버</t>
+          <t>거대 황금 크리스탈</t>
         </is>
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>Elite Revolver</t>
+          <t>Huge Gold Crystal</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>Mine_Ore_Spec.Name_KR</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="2" t="inlineStr">
         <is>
-          <t>펌프액션 샷건</t>
+          <t>강제 광고 제거</t>
         </is>
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>Pump Shotgun</t>
+          <t>Remove Forced Ads</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
         <is>
-          <t>돌격소총</t>
+          <t>자동 전면 광고 제거 + 돼지저금통</t>
         </is>
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>Assault Rifle</t>
+          <t>No more forced ads + piggy bank</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="inlineStr">
         <is>
-          <t>매그넘</t>
+          <t>영구 3배 버프</t>
         </is>
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>Magnum</t>
+          <t>Permanent x3 Buff</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="inlineStr">
         <is>
-          <t>전투 샷건</t>
+          <t>공격력·돈 x3 영구 + 다이아 1,000</t>
         </is>
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>Combat Shotgun</t>
+          <t>Permanent x3 attack &amp; gold + 1,000 gems</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>중기관총</t>
+          <t>광산 티켓 확장</t>
         </is>
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>Heavy MG</t>
+          <t>Mine Ticket Pack</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="inlineStr">
         <is>
-          <t>관통 라이플</t>
+          <t>하루 광산 티켓 2 → 6 + 다이아 500</t>
         </is>
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>Piercing Rifle</t>
+          <t>Daily mine tickets 2 → 6 + 500 gems</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
         <is>
-          <t>황금 매그넘</t>
+          <t>핫딜 레이저 총알</t>
         </is>
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>Golden Magnum</t>
+          <t>Hot Deal: Laser Ammo</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
         <is>
-          <t>드래곤 샷건</t>
+          <t>레이저탄_S 즉시 지급</t>
         </is>
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>Dragon Shotgun</t>
+          <t>Get a Laser Round_S now</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="inlineStr">
         <is>
-          <t>미니건</t>
+          <t>30분 방치 골드 상자</t>
         </is>
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>Minigun</t>
+          <t>30-min Gold Chest</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Name</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
         <is>
-          <t>레일 라이플</t>
+          <t>현재 스테이지 기준 600마리 처치 골드</t>
         </is>
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>Rail Rifle</t>
+          <t>Gold of 600 zombies at your current stage</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
         <is>
-          <t>레이저 건</t>
+          <t>S 등급 레이저 건 즉시 지급</t>
         </is>
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>Laser Gun</t>
+          <t>Get an S grade Laser Gun now</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>(지금은 안 씀) Weapon_Master.Name</t>
+          <t>(지금은 안 씀) Shop_Products.Description</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="inlineStr">
         <is>
-          <t>미사일 런처</t>
+          <t>리볼버</t>
         </is>
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>Missile Launcher</t>
+          <t>Revolver</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
@@ -6217,12 +6217,12 @@
     <row r="341">
       <c r="A341" s="2" t="inlineStr">
         <is>
-          <t>플라즈마 레이저</t>
+          <t>소드오프 샷건</t>
         </is>
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>Plasma Laser</t>
+          <t>Sawed-off Shotgun</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
     <row r="342">
       <c r="A342" s="2" t="inlineStr">
         <is>
-          <t>다연장 미사일</t>
+          <t>우지</t>
         </is>
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>Multi Missile</t>
+          <t>Uzi</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
@@ -6251,12 +6251,12 @@
     <row r="343">
       <c r="A343" s="2" t="inlineStr">
         <is>
-          <t>오메가 레이저</t>
+          <t>상위 리볼버</t>
         </is>
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>Omega Laser</t>
+          <t>Elite Revolver</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
@@ -6268,12 +6268,12 @@
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
         <is>
-          <t>핵 미사일</t>
+          <t>펌프액션 샷건</t>
         </is>
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>Nuke Missile</t>
+          <t>Pump Shotgun</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
     <row r="345">
       <c r="A345" s="2" t="inlineStr">
         <is>
-          <t>하이퍼 레이저</t>
+          <t>돌격소총</t>
         </is>
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>Hyper Laser</t>
+          <t>Assault Rifle</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
@@ -6302,12 +6302,12 @@
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
         <is>
-          <t>전술 핵 미사일</t>
+          <t>매그넘</t>
         </is>
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>Tactical Nuke</t>
+          <t>Magnum</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
@@ -6319,12 +6319,12 @@
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
         <is>
-          <t>퀘이사 레이저</t>
+          <t>전투 샷건</t>
         </is>
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>Quasar Laser</t>
+          <t>Combat Shotgun</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
         <is>
-          <t>반물질 미사일</t>
+          <t>중기관총</t>
         </is>
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>Antimatter Missile</t>
+          <t>Heavy MG</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
     <row r="349">
       <c r="A349" s="2" t="inlineStr">
         <is>
-          <t>네뷸라 레이저</t>
+          <t>관통 라이플</t>
         </is>
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>Nebula Laser</t>
+          <t>Piercing Rifle</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
     <row r="350">
       <c r="A350" s="2" t="inlineStr">
         <is>
-          <t>중력자 미사일</t>
+          <t>황금 매그넘</t>
         </is>
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>Graviton Missile</t>
+          <t>Golden Magnum</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="351">
       <c r="A351" s="2" t="inlineStr">
         <is>
-          <t>노바 레이저</t>
+          <t>드래곤 샷건</t>
         </is>
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>Nova Laser</t>
+          <t>Dragon Shotgun</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
@@ -6404,12 +6404,12 @@
     <row r="352">
       <c r="A352" s="2" t="inlineStr">
         <is>
-          <t>초신성 미사일</t>
+          <t>미니건</t>
         </is>
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>Supernova Missile</t>
+          <t>Minigun</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
@@ -6421,12 +6421,12 @@
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
         <is>
-          <t>보이드 레이저</t>
+          <t>레일 라이플</t>
         </is>
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>Void Laser</t>
+          <t>Rail Rifle</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
@@ -6438,12 +6438,12 @@
     <row r="354">
       <c r="A354" s="2" t="inlineStr">
         <is>
-          <t>차원파괴 미사일</t>
+          <t>레이저 건</t>
         </is>
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>Rift Missile</t>
+          <t>Laser Gun</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
     <row r="355">
       <c r="A355" s="2" t="inlineStr">
         <is>
-          <t>제네시스 레이저</t>
+          <t>미사일 런처</t>
         </is>
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>Genesis Laser</t>
+          <t>Missile Launcher</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
@@ -6472,15 +6472,270 @@
     <row r="356">
       <c r="A356" s="2" t="inlineStr">
         <is>
+          <t>플라즈마 레이저</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Plasma Laser</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>다연장 미사일</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Multi Missile</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>오메가 레이저</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Omega Laser</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>핵 미사일</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Nuke Missile</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>하이퍼 레이저</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Hyper Laser</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>전술 핵 미사일</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>Tactical Nuke</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>퀘이사 레이저</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>Quasar Laser</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>반물질 미사일</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Antimatter Missile</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>네뷸라 레이저</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Nebula Laser</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>중력자 미사일</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Graviton Missile</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>노바 레이저</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Nova Laser</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>초신성 미사일</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Supernova Missile</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>보이드 레이저</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Void Laser</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>차원파괴 미사일</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Rift Missile</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>제네시스 레이저</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Genesis Laser</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>(지금은 안 씀) Weapon_Master.Name</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
           <t>아포칼립스 미사일</t>
         </is>
       </c>
-      <c r="B356" s="2" t="inlineStr">
+      <c r="B371" s="2" t="inlineStr">
         <is>
           <t>Apocalypse Missile</t>
         </is>
       </c>
-      <c r="C356" s="2" t="inlineStr">
+      <c r="C371" s="2" t="inlineStr">
         <is>
           <t>(지금은 안 씀) Weapon_Master.Name</t>
         </is>
